--- a/research/traditional_assets/database/data/new_zealand/new_zealand_real_estate_operations_services.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_real_estate_operations_services.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="nzse_nzl" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -594,79 +596,88 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-3.525179856115108</v>
+        <v>0.3307240704500978</v>
       </c>
       <c r="J2">
-        <v>-3.525179856115108</v>
+        <v>0.3307240704500978</v>
       </c>
       <c r="K2">
-        <v>12.7</v>
+        <v>24.7</v>
       </c>
       <c r="L2">
-        <v>30.45563549160671</v>
+        <v>4.833659491193737</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.01378002528445007</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.04412955465587045</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.01378002528445007</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.04412955465587045</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>0.007901390644753477</v>
       </c>
       <c r="X2">
-        <v>0.04016054270822404</v>
+        <v>0.09049409899530525</v>
       </c>
       <c r="AB2">
-        <v>0.04016054270822404</v>
+        <v>0.06553874774702853</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>62.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>62.7</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>62.075</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>0.4421720733427362</v>
+      </c>
+      <c r="AI2">
+        <v>0.3506711409395973</v>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>0.4397024969010094</v>
+      </c>
+      <c r="AK2">
+        <v>0.3483934334221973</v>
       </c>
       <c r="AL2">
-        <v>0.095</v>
+        <v>1.5</v>
       </c>
       <c r="AM2">
-        <v>-0.006999999999999992</v>
+        <v>0.47</v>
       </c>
       <c r="AO2">
-        <v>-15.47368421052632</v>
+        <v>1.126666666666667</v>
       </c>
       <c r="AQ2">
-        <v>210.0000000000002</v>
+        <v>3.595744680851064</v>
       </c>
     </row>
     <row r="3">
@@ -692,79 +703,8800 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-3.525179856115108</v>
+        <v>0.3307240704500978</v>
       </c>
       <c r="J3">
-        <v>-3.525179856115108</v>
+        <v>0.3307240704500978</v>
       </c>
       <c r="K3">
-        <v>12.7</v>
+        <v>24.7</v>
       </c>
       <c r="L3">
-        <v>30.45563549160671</v>
+        <v>4.833659491193737</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>1.09</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.01378002528445007</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.04412955465587045</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>1.09</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.01378002528445007</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.04412955465587045</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.007901390644753477</v>
       </c>
       <c r="X3">
-        <v>0.04016054270822404</v>
+        <v>0.09049409899530525</v>
       </c>
       <c r="AB3">
-        <v>0.04016054270822404</v>
+        <v>0.06553874774702853</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>62.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>62.7</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>62.075</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.4421720733427362</v>
+      </c>
+      <c r="AI3">
+        <v>0.3506711409395973</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>0.4397024969010094</v>
+      </c>
+      <c r="AK3">
+        <v>0.3483934334221973</v>
       </c>
       <c r="AL3">
-        <v>0.095</v>
+        <v>1.5</v>
       </c>
       <c r="AM3">
-        <v>-0.006999999999999992</v>
+        <v>0.47</v>
       </c>
       <c r="AO3">
-        <v>-15.47368421052632</v>
+        <v>1.126666666666667</v>
       </c>
       <c r="AQ3">
-        <v>210.0000000000002</v>
+        <v>3.595744680851064</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>New Zealand Rural Land Company Limited (NZSE:NZL)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NZSE:NZL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Real Estate (Operations &amp; Services)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.442172073342736</v>
+      </c>
+      <c r="F2">
+        <v>0.04</v>
+      </c>
+      <c r="G2">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="H2">
+        <v>110.836480063049</v>
+      </c>
+      <c r="I2">
+        <v>141.175</v>
+      </c>
+      <c r="J2">
+        <v>115.883480063049</v>
+      </c>
+      <c r="K2">
+        <v>62.7</v>
+      </c>
+      <c r="L2">
+        <v>5.672</v>
+      </c>
+      <c r="M2">
+        <v>0.0655387477470285</v>
+      </c>
+      <c r="N2">
+        <v>0.07137446800124531</v>
+      </c>
+      <c r="O2">
+        <v>0.034056</v>
+      </c>
+      <c r="P2">
+        <v>0.0396</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.09049409899530519</v>
+      </c>
+      <c r="T2">
+        <v>0.0726984041679639</v>
+      </c>
+      <c r="U2">
+        <v>0.874061524010309</v>
+      </c>
+      <c r="V2">
+        <v>0.5731658232646401</v>
+      </c>
+      <c r="W2">
+        <v>5.417361200153866</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="AB2">
+        <v>0.0591424031092525</v>
+      </c>
+      <c r="AC2">
+        <v>0.0473</v>
+      </c>
+      <c r="AD2">
+        <v>0.2799999999999999</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>-1.69</v>
+      </c>
+      <c r="AI2">
+        <v>-1.577</v>
+      </c>
+      <c r="AJ2">
+        <v>62.7</v>
+      </c>
+      <c r="AK2">
+        <v>62.7</v>
+      </c>
+      <c r="AL2">
+        <v>1.5</v>
+      </c>
+      <c r="AM2">
+        <v>62.70000000000001</v>
+      </c>
+      <c r="AN2">
+        <v>0.625</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.07171107200773193</v>
+      </c>
+      <c r="C2">
+        <v>115.3232605823327</v>
+      </c>
+      <c r="D2">
+        <v>114.6982605823327</v>
+      </c>
+      <c r="E2">
+        <v>-62.7</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0.625</v>
+      </c>
+      <c r="H2">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>-1.69</v>
+      </c>
+      <c r="L2">
+        <v>1.69</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>1.69</v>
+      </c>
+      <c r="O2">
+        <v>0.4731999999999998</v>
+      </c>
+      <c r="P2">
+        <v>1.2168</v>
+      </c>
+      <c r="Q2">
+        <v>-0.4731999999999998</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.07171107200773193</v>
+      </c>
+      <c r="T2">
+        <v>0.5564716730724656</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.2799999999999999</v>
+      </c>
+      <c r="W2">
+        <v>0.03290400000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.07155996100611027</v>
+      </c>
+      <c r="C3">
+        <v>114.4343262011113</v>
+      </c>
+      <c r="D3">
+        <v>115.2273262011113</v>
+      </c>
+      <c r="E3">
+        <v>-61.282</v>
+      </c>
+      <c r="F3">
+        <v>1.418</v>
+      </c>
+      <c r="G3">
+        <v>0.625</v>
+      </c>
+      <c r="H3">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>-1.69</v>
+      </c>
+      <c r="L3">
+        <v>1.69</v>
+      </c>
+      <c r="M3">
+        <v>0.06480260000000002</v>
+      </c>
+      <c r="N3">
+        <v>1.6251974</v>
+      </c>
+      <c r="O3">
+        <v>0.4550552719999998</v>
+      </c>
+      <c r="P3">
+        <v>1.170142128</v>
+      </c>
+      <c r="Q3">
+        <v>-0.5198578719999998</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.07195042525869724</v>
+      </c>
+      <c r="T3">
+        <v>0.5605187397857199</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.2799999999999999</v>
+      </c>
+      <c r="W3">
+        <v>0.03290400000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>26.07920052590482</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.07140885000448863</v>
+      </c>
+      <c r="C4">
+        <v>113.5502952516616</v>
+      </c>
+      <c r="D4">
+        <v>115.7612952516616</v>
+      </c>
+      <c r="E4">
+        <v>-59.864</v>
+      </c>
+      <c r="F4">
+        <v>2.836</v>
+      </c>
+      <c r="G4">
+        <v>0.625</v>
+      </c>
+      <c r="H4">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>-1.69</v>
+      </c>
+      <c r="L4">
+        <v>1.69</v>
+      </c>
+      <c r="M4">
+        <v>0.1296052</v>
+      </c>
+      <c r="N4">
+        <v>1.5603948</v>
+      </c>
+      <c r="O4">
+        <v>0.4369105439999998</v>
+      </c>
+      <c r="P4">
+        <v>1.123484256</v>
+      </c>
+      <c r="Q4">
+        <v>-0.5665157439999999</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.07219466326988636</v>
+      </c>
+      <c r="T4">
+        <v>0.5646483996972038</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.2799999999999999</v>
+      </c>
+      <c r="W4">
+        <v>0.03290400000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>13.03960026295241</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.07141541900286698</v>
+      </c>
+      <c r="C5">
+        <v>112.108980028861</v>
+      </c>
+      <c r="D5">
+        <v>115.737980028861</v>
+      </c>
+      <c r="E5">
+        <v>-58.44600000000001</v>
+      </c>
+      <c r="F5">
+        <v>4.254</v>
+      </c>
+      <c r="G5">
+        <v>0.625</v>
+      </c>
+      <c r="H5">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>-1.69</v>
+      </c>
+      <c r="L5">
+        <v>1.69</v>
+      </c>
+      <c r="M5">
+        <v>0.2254620000000001</v>
+      </c>
+      <c r="N5">
+        <v>1.464538</v>
+      </c>
+      <c r="O5">
+        <v>0.4100706399999998</v>
+      </c>
+      <c r="P5">
+        <v>1.05446736</v>
+      </c>
+      <c r="Q5">
+        <v>-0.6355326399999999</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.07244393711635772</v>
+      </c>
+      <c r="T5">
+        <v>0.5688632072357288</v>
+      </c>
+      <c r="U5">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V5">
+        <v>0.2799999999999999</v>
+      </c>
+      <c r="W5">
+        <v>0.03816000000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>7.495719899583963</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.07137446800124533</v>
+      </c>
+      <c r="C6">
+        <v>110.8364800630494</v>
+      </c>
+      <c r="D6">
+        <v>115.8834800630494</v>
+      </c>
+      <c r="E6">
+        <v>-57.02800000000001</v>
+      </c>
+      <c r="F6">
+        <v>5.672000000000001</v>
+      </c>
+      <c r="G6">
+        <v>0.625</v>
+      </c>
+      <c r="H6">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>-1.69</v>
+      </c>
+      <c r="L6">
+        <v>1.69</v>
+      </c>
+      <c r="M6">
+        <v>0.31196</v>
+      </c>
+      <c r="N6">
+        <v>1.37804</v>
+      </c>
+      <c r="O6">
+        <v>0.3858511999999998</v>
+      </c>
+      <c r="P6">
+        <v>0.9921888000000001</v>
+      </c>
+      <c r="Q6">
+        <v>-0.6978111999999999</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.07269840416796389</v>
+      </c>
+      <c r="T6">
+        <v>0.5731658232646396</v>
+      </c>
+      <c r="U6">
+        <v>0.055</v>
+      </c>
+      <c r="V6">
+        <v>0.2799999999999999</v>
+      </c>
+      <c r="W6">
+        <v>0.0396</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>5.417361200153866</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.07142711699962367</v>
+      </c>
+      <c r="C7">
+        <v>109.2314837938422</v>
+      </c>
+      <c r="D7">
+        <v>115.6964837938422</v>
+      </c>
+      <c r="E7">
+        <v>-55.61</v>
+      </c>
+      <c r="F7">
+        <v>7.090000000000001</v>
+      </c>
+      <c r="G7">
+        <v>0.625</v>
+      </c>
+      <c r="H7">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>-1.69</v>
+      </c>
+      <c r="L7">
+        <v>1.69</v>
+      </c>
+      <c r="M7">
+        <v>0.4168920000000001</v>
+      </c>
+      <c r="N7">
+        <v>1.273108</v>
+      </c>
+      <c r="O7">
+        <v>0.3564702399999999</v>
+      </c>
+      <c r="P7">
+        <v>0.91663776</v>
+      </c>
+      <c r="Q7">
+        <v>-0.77336224</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.0729582284206565</v>
+      </c>
+      <c r="T7">
+        <v>0.5775590206836326</v>
+      </c>
+      <c r="U7">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V7">
+        <v>0.2799999999999999</v>
+      </c>
+      <c r="W7">
+        <v>0.04233600000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>4.053807700795408</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.07277864599800203</v>
+      </c>
+      <c r="C8">
+        <v>103.2115596068989</v>
+      </c>
+      <c r="D8">
+        <v>111.0945596068989</v>
+      </c>
+      <c r="E8">
+        <v>-54.192</v>
+      </c>
+      <c r="F8">
+        <v>8.508000000000001</v>
+      </c>
+      <c r="G8">
+        <v>0.625</v>
+      </c>
+      <c r="H8">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>-1.69</v>
+      </c>
+      <c r="L8">
+        <v>1.69</v>
+      </c>
+      <c r="M8">
+        <v>0.7776312000000002</v>
+      </c>
+      <c r="N8">
+        <v>0.9123687999999998</v>
+      </c>
+      <c r="O8">
+        <v>0.2554632639999999</v>
+      </c>
+      <c r="P8">
+        <v>0.6569055359999999</v>
+      </c>
+      <c r="Q8">
+        <v>-1.033094464</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.07322358084893833</v>
+      </c>
+      <c r="T8">
+        <v>0.5820456903881364</v>
+      </c>
+      <c r="U8">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V8">
+        <v>0.2799999999999999</v>
+      </c>
+      <c r="W8">
+        <v>0.06580800000000002</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>2.173266710492068</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.07402001499638036</v>
+      </c>
+      <c r="C9">
+        <v>97.87790703836163</v>
+      </c>
+      <c r="D9">
+        <v>107.1789070383616</v>
+      </c>
+      <c r="E9">
+        <v>-52.774</v>
+      </c>
+      <c r="F9">
+        <v>9.926000000000002</v>
+      </c>
+      <c r="G9">
+        <v>0.625</v>
+      </c>
+      <c r="H9">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>-1.69</v>
+      </c>
+      <c r="L9">
+        <v>1.69</v>
+      </c>
+      <c r="M9">
+        <v>1.116675</v>
+      </c>
+      <c r="N9">
+        <v>0.5733249999999996</v>
+      </c>
+      <c r="O9">
+        <v>0.1605309999999998</v>
+      </c>
+      <c r="P9">
+        <v>0.4127939999999998</v>
+      </c>
+      <c r="Q9">
+        <v>-1.277206</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.07349463978105417</v>
+      </c>
+      <c r="T9">
+        <v>0.5866288476131669</v>
+      </c>
+      <c r="U9">
+        <v>0.1125</v>
+      </c>
+      <c r="V9">
+        <v>0.2799999999999999</v>
+      </c>
+      <c r="W9">
+        <v>0.08100000000000002</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>1.513421541630286</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.08186028547212801</v>
+      </c>
+      <c r="C10">
+        <v>76.94513579933479</v>
+      </c>
+      <c r="D10">
+        <v>87.6641357993348</v>
+      </c>
+      <c r="E10">
+        <v>-51.356</v>
+      </c>
+      <c r="F10">
+        <v>11.344</v>
+      </c>
+      <c r="G10">
+        <v>0.625</v>
+      </c>
+      <c r="H10">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>-1.69</v>
+      </c>
+      <c r="L10">
+        <v>1.69</v>
+      </c>
+      <c r="M10">
+        <v>2.4253472</v>
+      </c>
+      <c r="N10">
+        <v>-0.7353472000000001</v>
+      </c>
+      <c r="O10">
+        <v>-0.205897216</v>
+      </c>
+      <c r="P10">
+        <v>-0.5294499840000001</v>
+      </c>
+      <c r="Q10">
+        <v>-2.219449984</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.07401454344719868</v>
+      </c>
+      <c r="T10">
+        <v>0.5954195567966286</v>
+      </c>
+      <c r="U10">
+        <v>0.2138</v>
+      </c>
+      <c r="V10">
+        <v>0.1951060862543721</v>
+      </c>
+      <c r="W10">
+        <v>0.1720863187588152</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>0.696807450908472</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.08361028547212801</v>
+      </c>
+      <c r="C11">
+        <v>72.10354150546988</v>
+      </c>
+      <c r="D11">
+        <v>84.24054150546988</v>
+      </c>
+      <c r="E11">
+        <v>-49.938</v>
+      </c>
+      <c r="F11">
+        <v>12.762</v>
+      </c>
+      <c r="G11">
+        <v>0.625</v>
+      </c>
+      <c r="H11">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>-1.69</v>
+      </c>
+      <c r="L11">
+        <v>1.69</v>
+      </c>
+      <c r="M11">
+        <v>2.7285156</v>
+      </c>
+      <c r="N11">
+        <v>-1.0385156</v>
+      </c>
+      <c r="O11">
+        <v>-0.290784368</v>
+      </c>
+      <c r="P11">
+        <v>-0.7477312320000002</v>
+      </c>
+      <c r="Q11">
+        <v>-2.437731232</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.07440151645211295</v>
+      </c>
+      <c r="T11">
+        <v>0.6019626288493388</v>
+      </c>
+      <c r="U11">
+        <v>0.2138</v>
+      </c>
+      <c r="V11">
+        <v>0.1734276322261085</v>
+      </c>
+      <c r="W11">
+        <v>0.176721172230058</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>0.6193844008075307</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.08536028547212801</v>
+      </c>
+      <c r="C12">
+        <v>67.51930345216537</v>
+      </c>
+      <c r="D12">
+        <v>81.07430345216538</v>
+      </c>
+      <c r="E12">
+        <v>-48.52</v>
+      </c>
+      <c r="F12">
+        <v>14.18</v>
+      </c>
+      <c r="G12">
+        <v>0.625</v>
+      </c>
+      <c r="H12">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>-1.69</v>
+      </c>
+      <c r="L12">
+        <v>1.69</v>
+      </c>
+      <c r="M12">
+        <v>3.031684</v>
+      </c>
+      <c r="N12">
+        <v>-1.341684</v>
+      </c>
+      <c r="O12">
+        <v>-0.37567152</v>
+      </c>
+      <c r="P12">
+        <v>-0.9660124800000003</v>
+      </c>
+      <c r="Q12">
+        <v>-2.65601248</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.07479708885713643</v>
+      </c>
+      <c r="T12">
+        <v>0.6086511025032203</v>
+      </c>
+      <c r="U12">
+        <v>0.2138</v>
+      </c>
+      <c r="V12">
+        <v>0.1560848690034977</v>
+      </c>
+      <c r="W12">
+        <v>0.1804290550070522</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>0.5574459607267775</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.08711028547212801</v>
+      </c>
+      <c r="C13">
+        <v>63.1644540906946</v>
+      </c>
+      <c r="D13">
+        <v>78.1374540906946</v>
+      </c>
+      <c r="E13">
+        <v>-47.102</v>
+      </c>
+      <c r="F13">
+        <v>15.598</v>
+      </c>
+      <c r="G13">
+        <v>0.625</v>
+      </c>
+      <c r="H13">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>-1.69</v>
+      </c>
+      <c r="L13">
+        <v>1.69</v>
+      </c>
+      <c r="M13">
+        <v>3.3348524</v>
+      </c>
+      <c r="N13">
+        <v>-1.6448524</v>
+      </c>
+      <c r="O13">
+        <v>-0.4605586719999998</v>
+      </c>
+      <c r="P13">
+        <v>-1.184293728</v>
+      </c>
+      <c r="Q13">
+        <v>-2.874293728</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.07520155052968852</v>
+      </c>
+      <c r="T13">
+        <v>0.6154898789358407</v>
+      </c>
+      <c r="U13">
+        <v>0.2138</v>
+      </c>
+      <c r="V13">
+        <v>0.1418953354577252</v>
+      </c>
+      <c r="W13">
+        <v>0.1834627772791383</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>0.5067690552061614</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.09191406395164109</v>
+      </c>
+      <c r="C14">
+        <v>54.67949305478949</v>
+      </c>
+      <c r="D14">
+        <v>71.07049305478949</v>
+      </c>
+      <c r="E14">
+        <v>-45.684</v>
+      </c>
+      <c r="F14">
+        <v>17.016</v>
+      </c>
+      <c r="G14">
+        <v>0.625</v>
+      </c>
+      <c r="H14">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>-1.69</v>
+      </c>
+      <c r="L14">
+        <v>1.69</v>
+      </c>
+      <c r="M14">
+        <v>4.0634208</v>
+      </c>
+      <c r="N14">
+        <v>-2.3734208</v>
+      </c>
+      <c r="O14">
+        <v>-0.6645578239999999</v>
+      </c>
+      <c r="P14">
+        <v>-1.708862976</v>
+      </c>
+      <c r="Q14">
+        <v>-3.398862976</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.07567631642151804</v>
+      </c>
+      <c r="T14">
+        <v>0.6235173831776367</v>
+      </c>
+      <c r="U14">
+        <v>0.2388</v>
+      </c>
+      <c r="V14">
+        <v>0.1164536048050942</v>
+      </c>
+      <c r="W14">
+        <v>0.2109908791725435</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>0.4159057314467652</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.09391406395164112</v>
+      </c>
+      <c r="C15">
+        <v>50.68246011985114</v>
+      </c>
+      <c r="D15">
+        <v>68.49146011985114</v>
+      </c>
+      <c r="E15">
+        <v>-44.26600000000001</v>
+      </c>
+      <c r="F15">
+        <v>18.434</v>
+      </c>
+      <c r="G15">
+        <v>0.625</v>
+      </c>
+      <c r="H15">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>-1.69</v>
+      </c>
+      <c r="L15">
+        <v>1.69</v>
+      </c>
+      <c r="M15">
+        <v>4.402039200000001</v>
+      </c>
+      <c r="N15">
+        <v>-2.712039200000001</v>
+      </c>
+      <c r="O15">
+        <v>-0.759370976</v>
+      </c>
+      <c r="P15">
+        <v>-1.952668224000001</v>
+      </c>
+      <c r="Q15">
+        <v>-3.642668224000001</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.07610018212751252</v>
+      </c>
+      <c r="T15">
+        <v>0.6306842496509429</v>
+      </c>
+      <c r="U15">
+        <v>0.2388</v>
+      </c>
+      <c r="V15">
+        <v>0.1074956352047023</v>
+      </c>
+      <c r="W15">
+        <v>0.2131300423131171</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>0.383912982873937</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.09591406395164112</v>
+      </c>
+      <c r="C16">
+        <v>46.86605050298887</v>
+      </c>
+      <c r="D16">
+        <v>66.09305050298887</v>
+      </c>
+      <c r="E16">
+        <v>-42.848</v>
+      </c>
+      <c r="F16">
+        <v>19.852</v>
+      </c>
+      <c r="G16">
+        <v>0.625</v>
+      </c>
+      <c r="H16">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>-1.69</v>
+      </c>
+      <c r="L16">
+        <v>1.69</v>
+      </c>
+      <c r="M16">
+        <v>4.740657600000001</v>
+      </c>
+      <c r="N16">
+        <v>-3.050657600000001</v>
+      </c>
+      <c r="O16">
+        <v>-0.8541841280000001</v>
+      </c>
+      <c r="P16">
+        <v>-2.196473472000001</v>
+      </c>
+      <c r="Q16">
+        <v>-3.886473472000001</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.07653390517550684</v>
+      </c>
+      <c r="T16">
+        <v>0.6380177874375818</v>
+      </c>
+      <c r="U16">
+        <v>0.2388</v>
+      </c>
+      <c r="V16">
+        <v>0.0998173755472236</v>
+      </c>
+      <c r="W16">
+        <v>0.214963610719323</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>0.3564906269543701</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.09791406395164109</v>
+      </c>
+      <c r="C17">
+        <v>43.2119311741924</v>
+      </c>
+      <c r="D17">
+        <v>63.8569311741924</v>
+      </c>
+      <c r="E17">
+        <v>-41.43000000000001</v>
+      </c>
+      <c r="F17">
+        <v>21.27</v>
+      </c>
+      <c r="G17">
+        <v>0.625</v>
+      </c>
+      <c r="H17">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>-1.69</v>
+      </c>
+      <c r="L17">
+        <v>1.69</v>
+      </c>
+      <c r="M17">
+        <v>5.079276</v>
+      </c>
+      <c r="N17">
+        <v>-3.389276</v>
+      </c>
+      <c r="O17">
+        <v>-0.9489972799999997</v>
+      </c>
+      <c r="P17">
+        <v>-2.44027872</v>
+      </c>
+      <c r="Q17">
+        <v>-4.13027872</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.07697783347168927</v>
+      </c>
+      <c r="T17">
+        <v>0.6455238790544945</v>
+      </c>
+      <c r="U17">
+        <v>0.2388</v>
+      </c>
+      <c r="V17">
+        <v>0.09316288384407538</v>
+      </c>
+      <c r="W17">
+        <v>0.2165527033380348</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>0.3327245851574122</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.09991406395164111</v>
+      </c>
+      <c r="C18">
+        <v>39.70416894778499</v>
+      </c>
+      <c r="D18">
+        <v>61.76716894778499</v>
+      </c>
+      <c r="E18">
+        <v>-40.012</v>
+      </c>
+      <c r="F18">
+        <v>22.688</v>
+      </c>
+      <c r="G18">
+        <v>0.625</v>
+      </c>
+      <c r="H18">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>-1.69</v>
+      </c>
+      <c r="L18">
+        <v>1.69</v>
+      </c>
+      <c r="M18">
+        <v>5.417894400000001</v>
+      </c>
+      <c r="N18">
+        <v>-3.727894400000001</v>
+      </c>
+      <c r="O18">
+        <v>-1.043810432</v>
+      </c>
+      <c r="P18">
+        <v>-2.684083968000001</v>
+      </c>
+      <c r="Q18">
+        <v>-4.374083968000001</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.07743233148920939</v>
+      </c>
+      <c r="T18">
+        <v>0.6532086871384766</v>
+      </c>
+      <c r="U18">
+        <v>0.2388</v>
+      </c>
+      <c r="V18">
+        <v>0.08734020360382067</v>
+      </c>
+      <c r="W18">
+        <v>0.2179431593794076</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>0.3119292985850739</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1019140639516411</v>
+      </c>
+      <c r="C19">
+        <v>36.32885024318972</v>
+      </c>
+      <c r="D19">
+        <v>59.80985024318972</v>
+      </c>
+      <c r="E19">
+        <v>-38.59399999999999</v>
+      </c>
+      <c r="F19">
+        <v>24.10600000000001</v>
+      </c>
+      <c r="G19">
+        <v>0.625</v>
+      </c>
+      <c r="H19">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>-1.69</v>
+      </c>
+      <c r="L19">
+        <v>1.69</v>
+      </c>
+      <c r="M19">
+        <v>5.756512800000001</v>
+      </c>
+      <c r="N19">
+        <v>-4.066512800000002</v>
+      </c>
+      <c r="O19">
+        <v>-1.138623584</v>
+      </c>
+      <c r="P19">
+        <v>-2.927889216000001</v>
+      </c>
+      <c r="Q19">
+        <v>-4.617889216000002</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.07789778126618781</v>
+      </c>
+      <c r="T19">
+        <v>0.6610786713208678</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>0.0822025445683018</v>
+      </c>
+      <c r="W19">
+        <v>0.2191700323570895</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>0.2935805163153635</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1039140639516411</v>
+      </c>
+      <c r="C20">
+        <v>33.07377092073769</v>
+      </c>
+      <c r="D20">
+        <v>57.97277092073769</v>
+      </c>
+      <c r="E20">
+        <v>-37.176</v>
+      </c>
+      <c r="F20">
+        <v>25.524</v>
+      </c>
+      <c r="G20">
+        <v>0.625</v>
+      </c>
+      <c r="H20">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>-1.69</v>
+      </c>
+      <c r="L20">
+        <v>1.69</v>
+      </c>
+      <c r="M20">
+        <v>6.095131200000001</v>
+      </c>
+      <c r="N20">
+        <v>-4.405131200000001</v>
+      </c>
+      <c r="O20">
+        <v>-1.233436736</v>
+      </c>
+      <c r="P20">
+        <v>-3.171694464000002</v>
+      </c>
+      <c r="Q20">
+        <v>-4.861694464000001</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.07837458347675108</v>
+      </c>
+      <c r="T20">
+        <v>0.669140606336976</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>0.07763573653672948</v>
+      </c>
+      <c r="W20">
+        <v>0.220260586115029</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.2772704876311767</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1059140639516411</v>
+      </c>
+      <c r="C21">
+        <v>29.92818157485901</v>
+      </c>
+      <c r="D21">
+        <v>56.24518157485901</v>
+      </c>
+      <c r="E21">
+        <v>-35.758</v>
+      </c>
+      <c r="F21">
+        <v>26.942</v>
+      </c>
+      <c r="G21">
+        <v>0.625</v>
+      </c>
+      <c r="H21">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>-1.69</v>
+      </c>
+      <c r="L21">
+        <v>1.69</v>
+      </c>
+      <c r="M21">
+        <v>6.433749600000001</v>
+      </c>
+      <c r="N21">
+        <v>-4.743749600000001</v>
+      </c>
+      <c r="O21">
+        <v>-1.328249888</v>
+      </c>
+      <c r="P21">
+        <v>-3.415499712000001</v>
+      </c>
+      <c r="Q21">
+        <v>-5.105499712</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.07886315858140232</v>
+      </c>
+      <c r="T21">
+        <v>0.6774016014769386</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>0.0735496451400595</v>
+      </c>
+      <c r="W21">
+        <v>0.2212363447405538</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.2626773040716412</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1079140639516411</v>
+      </c>
+      <c r="C22">
+        <v>26.88257705100367</v>
+      </c>
+      <c r="D22">
+        <v>54.61757705100367</v>
+      </c>
+      <c r="E22">
+        <v>-34.34</v>
+      </c>
+      <c r="F22">
+        <v>28.36</v>
+      </c>
+      <c r="G22">
+        <v>0.625</v>
+      </c>
+      <c r="H22">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>-1.69</v>
+      </c>
+      <c r="L22">
+        <v>1.69</v>
+      </c>
+      <c r="M22">
+        <v>6.772368000000001</v>
+      </c>
+      <c r="N22">
+        <v>-5.082368000000001</v>
+      </c>
+      <c r="O22">
+        <v>-1.42306304</v>
+      </c>
+      <c r="P22">
+        <v>-3.659304960000001</v>
+      </c>
+      <c r="Q22">
+        <v>-5.349304960000001</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.07936394806366985</v>
+      </c>
+      <c r="T22">
+        <v>0.6858691214954004</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>0.06987216288305653</v>
+      </c>
+      <c r="W22">
+        <v>0.2221145275035261</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.2495434388680592</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1099140639516411</v>
+      </c>
+      <c r="C23">
+        <v>23.92852148010718</v>
+      </c>
+      <c r="D23">
+        <v>53.08152148010718</v>
+      </c>
+      <c r="E23">
+        <v>-32.922</v>
+      </c>
+      <c r="F23">
+        <v>29.778</v>
+      </c>
+      <c r="G23">
+        <v>0.625</v>
+      </c>
+      <c r="H23">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>-1.69</v>
+      </c>
+      <c r="L23">
+        <v>1.69</v>
+      </c>
+      <c r="M23">
+        <v>7.110986400000001</v>
+      </c>
+      <c r="N23">
+        <v>-5.4209864</v>
+      </c>
+      <c r="O23">
+        <v>-1.517876192</v>
+      </c>
+      <c r="P23">
+        <v>-3.903110208000001</v>
+      </c>
+      <c r="Q23">
+        <v>-5.593110208000001</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.07987741576067833</v>
+      </c>
+      <c r="T23">
+        <v>0.6945510091092663</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>0.06654491703148241</v>
+      </c>
+      <c r="W23">
+        <v>0.222909073812882</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.2376604179695802</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1119140639516411</v>
+      </c>
+      <c r="C24">
+        <v>21.05850202964369</v>
+      </c>
+      <c r="D24">
+        <v>51.62950202964369</v>
+      </c>
+      <c r="E24">
+        <v>-31.504</v>
+      </c>
+      <c r="F24">
+        <v>31.196</v>
+      </c>
+      <c r="G24">
+        <v>0.625</v>
+      </c>
+      <c r="H24">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>-1.69</v>
+      </c>
+      <c r="L24">
+        <v>1.69</v>
+      </c>
+      <c r="M24">
+        <v>7.4496048</v>
+      </c>
+      <c r="N24">
+        <v>-5.7596048</v>
+      </c>
+      <c r="O24">
+        <v>-1.612689343999999</v>
+      </c>
+      <c r="P24">
+        <v>-4.146915456</v>
+      </c>
+      <c r="Q24">
+        <v>-5.836915456</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.08040404929607164</v>
+      </c>
+      <c r="T24">
+        <v>0.7034555092260516</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>0.06352014807550593</v>
+      </c>
+      <c r="W24">
+        <v>0.2236313886395692</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.2268576716982357</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1139140639516411</v>
+      </c>
+      <c r="C25">
+        <v>18.26580601897695</v>
+      </c>
+      <c r="D25">
+        <v>50.25480601897695</v>
+      </c>
+      <c r="E25">
+        <v>-30.086</v>
+      </c>
+      <c r="F25">
+        <v>32.614</v>
+      </c>
+      <c r="G25">
+        <v>0.625</v>
+      </c>
+      <c r="H25">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>-1.69</v>
+      </c>
+      <c r="L25">
+        <v>1.69</v>
+      </c>
+      <c r="M25">
+        <v>7.788223200000002</v>
+      </c>
+      <c r="N25">
+        <v>-6.098223200000001</v>
+      </c>
+      <c r="O25">
+        <v>-1.707502496</v>
+      </c>
+      <c r="P25">
+        <v>-4.390720704000001</v>
+      </c>
+      <c r="Q25">
+        <v>-6.080720704000001</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.08094436162459205</v>
+      </c>
+      <c r="T25">
+        <v>0.7125912950601563</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>0.06075840250700567</v>
+      </c>
+      <c r="W25">
+        <v>0.2242908934813271</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.2169942946678776</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1159140639516411</v>
+      </c>
+      <c r="C26">
+        <v>15.54441715723853</v>
+      </c>
+      <c r="D26">
+        <v>48.95141715723853</v>
+      </c>
+      <c r="E26">
+        <v>-28.668</v>
+      </c>
+      <c r="F26">
+        <v>34.032</v>
+      </c>
+      <c r="G26">
+        <v>0.625</v>
+      </c>
+      <c r="H26">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>-1.69</v>
+      </c>
+      <c r="L26">
+        <v>1.69</v>
+      </c>
+      <c r="M26">
+        <v>8.126841600000001</v>
+      </c>
+      <c r="N26">
+        <v>-6.436841600000001</v>
+      </c>
+      <c r="O26">
+        <v>-1.802315648</v>
+      </c>
+      <c r="P26">
+        <v>-4.634525952000002</v>
+      </c>
+      <c r="Q26">
+        <v>-6.324525952000002</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.08149889269859983</v>
+      </c>
+      <c r="T26">
+        <v>0.7219674963109477</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>0.05822680240254711</v>
+      </c>
+      <c r="W26">
+        <v>0.2248954395862718</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.2079528657233826</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1179140639516411</v>
+      </c>
+      <c r="C27">
+        <v>12.88892751981678</v>
+      </c>
+      <c r="D27">
+        <v>47.71392751981678</v>
+      </c>
+      <c r="E27">
+        <v>-27.25</v>
+      </c>
+      <c r="F27">
+        <v>35.45</v>
+      </c>
+      <c r="G27">
+        <v>0.625</v>
+      </c>
+      <c r="H27">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>-1.69</v>
+      </c>
+      <c r="L27">
+        <v>1.69</v>
+      </c>
+      <c r="M27">
+        <v>8.465460000000002</v>
+      </c>
+      <c r="N27">
+        <v>-6.775460000000002</v>
+      </c>
+      <c r="O27">
+        <v>-1.8971288</v>
+      </c>
+      <c r="P27">
+        <v>-4.878331200000003</v>
+      </c>
+      <c r="Q27">
+        <v>-6.568331200000003</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.08206821126791451</v>
+      </c>
+      <c r="T27">
+        <v>0.7315937295950938</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>0.05589773030644522</v>
+      </c>
+      <c r="W27">
+        <v>0.2254516220028209</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.1996347510944472</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1199140639516411</v>
+      </c>
+      <c r="C28">
+        <v>10.29446254702825</v>
+      </c>
+      <c r="D28">
+        <v>46.53746254702826</v>
+      </c>
+      <c r="E28">
+        <v>-25.832</v>
+      </c>
+      <c r="F28">
+        <v>36.868</v>
+      </c>
+      <c r="G28">
+        <v>0.625</v>
+      </c>
+      <c r="H28">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>-1.69</v>
+      </c>
+      <c r="L28">
+        <v>1.69</v>
+      </c>
+      <c r="M28">
+        <v>8.804078400000002</v>
+      </c>
+      <c r="N28">
+        <v>-7.114078400000002</v>
+      </c>
+      <c r="O28">
+        <v>-1.991941952</v>
+      </c>
+      <c r="P28">
+        <v>-5.122136448000003</v>
+      </c>
+      <c r="Q28">
+        <v>-6.812136448000002</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.08265291682558903</v>
+      </c>
+      <c r="T28">
+        <v>0.7414801313463788</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>0.05374781760235117</v>
+      </c>
+      <c r="W28">
+        <v>0.2259650211565586</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.1919564914369685</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1219140639516411</v>
+      </c>
+      <c r="C29">
+        <v>7.756616871473128</v>
+      </c>
+      <c r="D29">
+        <v>45.41761687147314</v>
+      </c>
+      <c r="E29">
+        <v>-24.41399999999999</v>
+      </c>
+      <c r="F29">
+        <v>38.28600000000001</v>
+      </c>
+      <c r="G29">
+        <v>0.625</v>
+      </c>
+      <c r="H29">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>-1.69</v>
+      </c>
+      <c r="L29">
+        <v>1.69</v>
+      </c>
+      <c r="M29">
+        <v>9.142696800000003</v>
+      </c>
+      <c r="N29">
+        <v>-7.452696800000004</v>
+      </c>
+      <c r="O29">
+        <v>-2.086755104</v>
+      </c>
+      <c r="P29">
+        <v>-5.365941696000004</v>
+      </c>
+      <c r="Q29">
+        <v>-7.055941696000003</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.0832536417136108</v>
+      </c>
+      <c r="T29">
+        <v>0.7516373934196169</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>0.05175715769115297</v>
+      </c>
+      <c r="W29">
+        <v>0.2264403907433527</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.1848469917541178</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1239140639516411</v>
+      </c>
+      <c r="C30">
+        <v>5.271399192917023</v>
+      </c>
+      <c r="D30">
+        <v>44.35039919291703</v>
+      </c>
+      <c r="E30">
+        <v>-22.996</v>
+      </c>
+      <c r="F30">
+        <v>39.70400000000001</v>
+      </c>
+      <c r="G30">
+        <v>0.625</v>
+      </c>
+      <c r="H30">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>-1.69</v>
+      </c>
+      <c r="L30">
+        <v>1.69</v>
+      </c>
+      <c r="M30">
+        <v>9.481315200000003</v>
+      </c>
+      <c r="N30">
+        <v>-7.791315200000003</v>
+      </c>
+      <c r="O30">
+        <v>-2.181568256</v>
+      </c>
+      <c r="P30">
+        <v>-5.609746944000003</v>
+      </c>
+      <c r="Q30">
+        <v>-7.299746944000002</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.08387105340407761</v>
+      </c>
+      <c r="T30">
+        <v>0.762076801661556</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>0.0499086877736118</v>
+      </c>
+      <c r="W30">
+        <v>0.2268818053596615</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.178245313477185</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1259140639516411</v>
+      </c>
+      <c r="C31">
+        <v>2.835184746681669</v>
+      </c>
+      <c r="D31">
+        <v>43.33218474668167</v>
+      </c>
+      <c r="E31">
+        <v>-21.578</v>
+      </c>
+      <c r="F31">
+        <v>41.122</v>
+      </c>
+      <c r="G31">
+        <v>0.625</v>
+      </c>
+      <c r="H31">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>-1.69</v>
+      </c>
+      <c r="L31">
+        <v>1.69</v>
+      </c>
+      <c r="M31">
+        <v>9.819933600000001</v>
+      </c>
+      <c r="N31">
+        <v>-8.129933600000001</v>
+      </c>
+      <c r="O31">
+        <v>-2.276381408</v>
+      </c>
+      <c r="P31">
+        <v>-5.853552192000001</v>
+      </c>
+      <c r="Q31">
+        <v>-7.543552192000002</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.08450585697314912</v>
+      </c>
+      <c r="T31">
+        <v>0.7728102777412962</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0.04818769854003899</v>
+      </c>
+      <c r="W31">
+        <v>0.2272927775886387</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.1720989233572822</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1279140639516411</v>
+      </c>
+      <c r="C32">
+        <v>0.4446741725887549</v>
+      </c>
+      <c r="D32">
+        <v>42.35967417258875</v>
+      </c>
+      <c r="E32">
+        <v>-20.16</v>
+      </c>
+      <c r="F32">
+        <v>42.54</v>
+      </c>
+      <c r="G32">
+        <v>0.625</v>
+      </c>
+      <c r="H32">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>-1.69</v>
+      </c>
+      <c r="L32">
+        <v>1.69</v>
+      </c>
+      <c r="M32">
+        <v>10.158552</v>
+      </c>
+      <c r="N32">
+        <v>-8.468552000000001</v>
+      </c>
+      <c r="O32">
+        <v>-2.371194559999999</v>
+      </c>
+      <c r="P32">
+        <v>-6.097357440000001</v>
+      </c>
+      <c r="Q32">
+        <v>-7.787357440000001</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.08515879778705127</v>
+      </c>
+      <c r="T32">
+        <v>0.7838504245661719</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0.04658144192203769</v>
+      </c>
+      <c r="W32">
+        <v>0.2276763516690174</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.1663622925787061</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1299140639516411</v>
+      </c>
+      <c r="C33">
+        <v>-1.903142199010524</v>
+      </c>
+      <c r="D33">
+        <v>41.42985780098948</v>
+      </c>
+      <c r="E33">
+        <v>-18.742</v>
+      </c>
+      <c r="F33">
+        <v>43.95800000000001</v>
+      </c>
+      <c r="G33">
+        <v>0.625</v>
+      </c>
+      <c r="H33">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>-1.69</v>
+      </c>
+      <c r="L33">
+        <v>1.69</v>
+      </c>
+      <c r="M33">
+        <v>10.4971704</v>
+      </c>
+      <c r="N33">
+        <v>-8.807170400000002</v>
+      </c>
+      <c r="O33">
+        <v>-2.466007712</v>
+      </c>
+      <c r="P33">
+        <v>-6.341162688000002</v>
+      </c>
+      <c r="Q33">
+        <v>-8.031162688000002</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.08583066442164622</v>
+      </c>
+      <c r="T33">
+        <v>0.7952105756468412</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.04507881476326227</v>
+      </c>
+      <c r="W33">
+        <v>0.228035179034533</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.160995767011651</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1319140639516411</v>
+      </c>
+      <c r="C34">
+        <v>-4.211015458596876</v>
+      </c>
+      <c r="D34">
+        <v>40.53998454140313</v>
+      </c>
+      <c r="E34">
+        <v>-17.324</v>
+      </c>
+      <c r="F34">
+        <v>45.376</v>
+      </c>
+      <c r="G34">
+        <v>0.625</v>
+      </c>
+      <c r="H34">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>-1.69</v>
+      </c>
+      <c r="L34">
+        <v>1.69</v>
+      </c>
+      <c r="M34">
+        <v>10.8357888</v>
+      </c>
+      <c r="N34">
+        <v>-9.145788800000002</v>
+      </c>
+      <c r="O34">
+        <v>-2.560820864</v>
+      </c>
+      <c r="P34">
+        <v>-6.584967936000002</v>
+      </c>
+      <c r="Q34">
+        <v>-8.274967936000001</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.08652229183961159</v>
+      </c>
+      <c r="T34">
+        <v>0.8069048488181182</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.04367010180191033</v>
+      </c>
+      <c r="W34">
+        <v>0.2283715796897038</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.1559646492925369</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1339140639516411</v>
+      </c>
+      <c r="C35">
+        <v>-6.481465303701071</v>
+      </c>
+      <c r="D35">
+        <v>39.68753469629893</v>
+      </c>
+      <c r="E35">
+        <v>-15.906</v>
+      </c>
+      <c r="F35">
+        <v>46.794</v>
+      </c>
+      <c r="G35">
+        <v>0.625</v>
+      </c>
+      <c r="H35">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>-1.69</v>
+      </c>
+      <c r="L35">
+        <v>1.69</v>
+      </c>
+      <c r="M35">
+        <v>11.1744072</v>
+      </c>
+      <c r="N35">
+        <v>-9.484407200000001</v>
+      </c>
+      <c r="O35">
+        <v>-2.655634016</v>
+      </c>
+      <c r="P35">
+        <v>-6.828773184000002</v>
+      </c>
+      <c r="Q35">
+        <v>-8.518773184000002</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.08723456485214312</v>
+      </c>
+      <c r="T35">
+        <v>0.8189482047706275</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.04234676538367062</v>
+      </c>
+      <c r="W35">
+        <v>0.2286875924263795</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.1512384477988237</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1359140639516411</v>
+      </c>
+      <c r="C36">
+        <v>-8.716803865828616</v>
+      </c>
+      <c r="D36">
+        <v>38.87019613417139</v>
+      </c>
+      <c r="E36">
+        <v>-14.48799999999999</v>
+      </c>
+      <c r="F36">
+        <v>48.21200000000001</v>
+      </c>
+      <c r="G36">
+        <v>0.625</v>
+      </c>
+      <c r="H36">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>-1.69</v>
+      </c>
+      <c r="L36">
+        <v>1.69</v>
+      </c>
+      <c r="M36">
+        <v>11.5130256</v>
+      </c>
+      <c r="N36">
+        <v>-9.823025600000003</v>
+      </c>
+      <c r="O36">
+        <v>-2.750447168</v>
+      </c>
+      <c r="P36">
+        <v>-7.072578432000003</v>
+      </c>
+      <c r="Q36">
+        <v>-8.762578432000003</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.08796842189535739</v>
+      </c>
+      <c r="T36">
+        <v>0.8313565109035157</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.0411012722841509</v>
+      </c>
+      <c r="W36">
+        <v>0.2289850161785448</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.1467902581576818</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1379140639516411</v>
+      </c>
+      <c r="C37">
+        <v>-10.91915665259634</v>
+      </c>
+      <c r="D37">
+        <v>38.08584334740367</v>
+      </c>
+      <c r="E37">
+        <v>-13.06999999999999</v>
+      </c>
+      <c r="F37">
+        <v>49.63000000000001</v>
+      </c>
+      <c r="G37">
+        <v>0.625</v>
+      </c>
+      <c r="H37">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>-1.69</v>
+      </c>
+      <c r="L37">
+        <v>1.69</v>
+      </c>
+      <c r="M37">
+        <v>11.851644</v>
+      </c>
+      <c r="N37">
+        <v>-10.161644</v>
+      </c>
+      <c r="O37">
+        <v>-2.84526032</v>
+      </c>
+      <c r="P37">
+        <v>-7.316383680000003</v>
+      </c>
+      <c r="Q37">
+        <v>-9.006383680000003</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.08872485915528597</v>
+      </c>
+      <c r="T37">
+        <v>0.844146611071262</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.03992695021888944</v>
+      </c>
+      <c r="W37">
+        <v>0.2292654442877292</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.142596250781748</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1399140639516411</v>
+      </c>
+      <c r="C38">
+        <v>-13.0904810045009</v>
+      </c>
+      <c r="D38">
+        <v>37.3325189954991</v>
+      </c>
+      <c r="E38">
+        <v>-11.652</v>
+      </c>
+      <c r="F38">
+        <v>51.048</v>
+      </c>
+      <c r="G38">
+        <v>0.625</v>
+      </c>
+      <c r="H38">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>-1.69</v>
+      </c>
+      <c r="L38">
+        <v>1.69</v>
+      </c>
+      <c r="M38">
+        <v>12.1902624</v>
+      </c>
+      <c r="N38">
+        <v>-10.5002624</v>
+      </c>
+      <c r="O38">
+        <v>-2.940073472</v>
+      </c>
+      <c r="P38">
+        <v>-7.560188928000002</v>
+      </c>
+      <c r="Q38">
+        <v>-9.250188928000002</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.08950493507958732</v>
+      </c>
+      <c r="T38">
+        <v>0.8573364018692504</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.03881786826836474</v>
+      </c>
+      <c r="W38">
+        <v>0.2295302930575145</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.1386352438155883</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1419140639516411</v>
+      </c>
+      <c r="C39">
+        <v>-15.23258240376313</v>
+      </c>
+      <c r="D39">
+        <v>36.60841759623688</v>
+      </c>
+      <c r="E39">
+        <v>-10.234</v>
+      </c>
+      <c r="F39">
+        <v>52.466</v>
+      </c>
+      <c r="G39">
+        <v>0.625</v>
+      </c>
+      <c r="H39">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>-1.69</v>
+      </c>
+      <c r="L39">
+        <v>1.69</v>
+      </c>
+      <c r="M39">
+        <v>12.5288808</v>
+      </c>
+      <c r="N39">
+        <v>-10.8388808</v>
+      </c>
+      <c r="O39">
+        <v>-3.034886623999999</v>
+      </c>
+      <c r="P39">
+        <v>-7.803994176000002</v>
+      </c>
+      <c r="Q39">
+        <v>-9.493994176000003</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.09030977531894585</v>
+      </c>
+      <c r="T39">
+        <v>0.8709449161846354</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.03776873669354407</v>
+      </c>
+      <c r="W39">
+        <v>0.2297808256775817</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.134888345334086</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1439140639516411</v>
+      </c>
+      <c r="C40">
+        <v>-17.34712892132674</v>
+      </c>
+      <c r="D40">
+        <v>35.91187107867326</v>
+      </c>
+      <c r="E40">
+        <v>-8.815999999999995</v>
+      </c>
+      <c r="F40">
+        <v>53.88400000000001</v>
+      </c>
+      <c r="G40">
+        <v>0.625</v>
+      </c>
+      <c r="H40">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>-1.69</v>
+      </c>
+      <c r="L40">
+        <v>1.69</v>
+      </c>
+      <c r="M40">
+        <v>12.8674992</v>
+      </c>
+      <c r="N40">
+        <v>-11.1774992</v>
+      </c>
+      <c r="O40">
+        <v>-3.129699776</v>
+      </c>
+      <c r="P40">
+        <v>-8.047799424000004</v>
+      </c>
+      <c r="Q40">
+        <v>-9.737799424000004</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.09114057814667079</v>
+      </c>
+      <c r="T40">
+        <v>0.8849924148327748</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.03677482257002975</v>
+      </c>
+      <c r="W40">
+        <v>0.2300181723702769</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.1313386520358205</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1459140639516411</v>
+      </c>
+      <c r="C41">
+        <v>-19.43566404535838</v>
+      </c>
+      <c r="D41">
+        <v>35.24133595464163</v>
+      </c>
+      <c r="E41">
+        <v>-7.397999999999996</v>
+      </c>
+      <c r="F41">
+        <v>55.30200000000001</v>
+      </c>
+      <c r="G41">
+        <v>0.625</v>
+      </c>
+      <c r="H41">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>-1.69</v>
+      </c>
+      <c r="L41">
+        <v>1.69</v>
+      </c>
+      <c r="M41">
+        <v>13.2061176</v>
+      </c>
+      <c r="N41">
+        <v>-11.5161176</v>
+      </c>
+      <c r="O41">
+        <v>-3.224512928</v>
+      </c>
+      <c r="P41">
+        <v>-8.291604672000004</v>
+      </c>
+      <c r="Q41">
+        <v>-9.981604672000003</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.0919986204113703</v>
+      </c>
+      <c r="T41">
+        <v>0.8995004872070825</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.03583187840156745</v>
+      </c>
+      <c r="W41">
+        <v>0.2302433474377057</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.1279709942913123</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1479140639516411</v>
+      </c>
+      <c r="C42">
+        <v>-21.4996180989121</v>
+      </c>
+      <c r="D42">
+        <v>34.5953819010879</v>
+      </c>
+      <c r="E42">
+        <v>-5.979999999999997</v>
+      </c>
+      <c r="F42">
+        <v>56.72000000000001</v>
+      </c>
+      <c r="G42">
+        <v>0.625</v>
+      </c>
+      <c r="H42">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>-1.69</v>
+      </c>
+      <c r="L42">
+        <v>1.69</v>
+      </c>
+      <c r="M42">
+        <v>13.544736</v>
+      </c>
+      <c r="N42">
+        <v>-11.854736</v>
+      </c>
+      <c r="O42">
+        <v>-3.31932608</v>
+      </c>
+      <c r="P42">
+        <v>-8.535409920000003</v>
+      </c>
+      <c r="Q42">
+        <v>-10.22540992</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.09288526408489313</v>
+      </c>
+      <c r="T42">
+        <v>0.9144921619938672</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.03493608144152827</v>
+      </c>
+      <c r="W42">
+        <v>0.2304572637517631</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.1247717194340295</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1499140639516411</v>
+      </c>
+      <c r="C43">
+        <v>-23.54031842451885</v>
+      </c>
+      <c r="D43">
+        <v>33.97268157548116</v>
+      </c>
+      <c r="E43">
+        <v>-4.561999999999991</v>
+      </c>
+      <c r="F43">
+        <v>58.13800000000001</v>
+      </c>
+      <c r="G43">
+        <v>0.625</v>
+      </c>
+      <c r="H43">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>-1.69</v>
+      </c>
+      <c r="L43">
+        <v>1.69</v>
+      </c>
+      <c r="M43">
+        <v>13.8833544</v>
+      </c>
+      <c r="N43">
+        <v>-12.1933544</v>
+      </c>
+      <c r="O43">
+        <v>-3.414139232</v>
+      </c>
+      <c r="P43">
+        <v>-8.779215168000004</v>
+      </c>
+      <c r="Q43">
+        <v>-10.469215168</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.09380196347616251</v>
+      </c>
+      <c r="T43">
+        <v>0.9299920291463056</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.03408398189417391</v>
+      </c>
+      <c r="W43">
+        <v>0.2306607451236713</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.1217285067649069</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1519140639516411</v>
+      </c>
+      <c r="C44">
+        <v>-25.5589984883172</v>
+      </c>
+      <c r="D44">
+        <v>33.3720015116828</v>
+      </c>
+      <c r="E44">
+        <v>-3.143999999999998</v>
+      </c>
+      <c r="F44">
+        <v>59.556</v>
+      </c>
+      <c r="G44">
+        <v>0.625</v>
+      </c>
+      <c r="H44">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>-1.69</v>
+      </c>
+      <c r="L44">
+        <v>1.69</v>
+      </c>
+      <c r="M44">
+        <v>14.2219728</v>
+      </c>
+      <c r="N44">
+        <v>-12.5319728</v>
+      </c>
+      <c r="O44">
+        <v>-3.508952384</v>
+      </c>
+      <c r="P44">
+        <v>-9.023020416000001</v>
+      </c>
+      <c r="Q44">
+        <v>-10.713020416</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.09475027319126875</v>
+      </c>
+      <c r="T44">
+        <v>0.9460263744764142</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.0332724585157412</v>
+      </c>
+      <c r="W44">
+        <v>0.230854536906441</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.11883020898479</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1539140639516411</v>
+      </c>
+      <c r="C45">
+        <v>-27.55680603512923</v>
+      </c>
+      <c r="D45">
+        <v>32.79219396487077</v>
+      </c>
+      <c r="E45">
+        <v>-1.725999999999999</v>
+      </c>
+      <c r="F45">
+        <v>60.974</v>
+      </c>
+      <c r="G45">
+        <v>0.625</v>
+      </c>
+      <c r="H45">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>-1.69</v>
+      </c>
+      <c r="L45">
+        <v>1.69</v>
+      </c>
+      <c r="M45">
+        <v>14.5605912</v>
+      </c>
+      <c r="N45">
+        <v>-12.8705912</v>
+      </c>
+      <c r="O45">
+        <v>-3.603765535999999</v>
+      </c>
+      <c r="P45">
+        <v>-9.266825664000002</v>
+      </c>
+      <c r="Q45">
+        <v>-10.956825664</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.09573185693146645</v>
+      </c>
+      <c r="T45">
+        <v>0.962623328414597</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.03249868041072397</v>
+      </c>
+      <c r="W45">
+        <v>0.2310393151179191</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.1160667157525856</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1559140639516411</v>
+      </c>
+      <c r="C46">
+        <v>-29.53481040793303</v>
+      </c>
+      <c r="D46">
+        <v>32.23218959206697</v>
+      </c>
+      <c r="E46">
+        <v>-0.3079999999999998</v>
+      </c>
+      <c r="F46">
+        <v>62.392</v>
+      </c>
+      <c r="G46">
+        <v>0.625</v>
+      </c>
+      <c r="H46">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>-1.69</v>
+      </c>
+      <c r="L46">
+        <v>1.69</v>
+      </c>
+      <c r="M46">
+        <v>14.8992096</v>
+      </c>
+      <c r="N46">
+        <v>-13.2092096</v>
+      </c>
+      <c r="O46">
+        <v>-3.698578687999999</v>
+      </c>
+      <c r="P46">
+        <v>-9.510630912000002</v>
+      </c>
+      <c r="Q46">
+        <v>-11.200630912</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.09674849723381407</v>
+      </c>
+      <c r="T46">
+        <v>0.9798130307077149</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.03176007403775297</v>
+      </c>
+      <c r="W46">
+        <v>0.2312156943197846</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.1134288358491178</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1579140639516411</v>
+      </c>
+      <c r="C47">
+        <v>-31.49400912994378</v>
+      </c>
+      <c r="D47">
+        <v>31.69099087005623</v>
+      </c>
+      <c r="E47">
+        <v>1.110000000000007</v>
+      </c>
+      <c r="F47">
+        <v>63.81000000000001</v>
+      </c>
+      <c r="G47">
+        <v>0.625</v>
+      </c>
+      <c r="H47">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>-1.69</v>
+      </c>
+      <c r="L47">
+        <v>1.69</v>
+      </c>
+      <c r="M47">
+        <v>15.237828</v>
+      </c>
+      <c r="N47">
+        <v>-13.547828</v>
+      </c>
+      <c r="O47">
+        <v>-3.79339184</v>
+      </c>
+      <c r="P47">
+        <v>-9.754436160000003</v>
+      </c>
+      <c r="Q47">
+        <v>-11.44443616</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.09780210627442887</v>
+      </c>
+      <c r="T47">
+        <v>0.9976278130842188</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.03105429461469179</v>
+      </c>
+      <c r="W47">
+        <v>0.2313842344460116</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.1109081950524707</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1599140639516411</v>
+      </c>
+      <c r="C48">
+        <v>-33.43533383454142</v>
+      </c>
+      <c r="D48">
+        <v>31.16766616545858</v>
+      </c>
+      <c r="E48">
+        <v>2.528000000000006</v>
+      </c>
+      <c r="F48">
+        <v>65.22800000000001</v>
+      </c>
+      <c r="G48">
+        <v>0.625</v>
+      </c>
+      <c r="H48">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>-1.69</v>
+      </c>
+      <c r="L48">
+        <v>1.69</v>
+      </c>
+      <c r="M48">
+        <v>15.5764464</v>
+      </c>
+      <c r="N48">
+        <v>-13.8864464</v>
+      </c>
+      <c r="O48">
+        <v>-3.888204992</v>
+      </c>
+      <c r="P48">
+        <v>-9.998241408000004</v>
+      </c>
+      <c r="Q48">
+        <v>-11.688241408</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.09889473787210348</v>
+      </c>
+      <c r="T48">
+        <v>1.016102402215408</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.03037920125350283</v>
+      </c>
+      <c r="W48">
+        <v>0.2315454467406635</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.1084971473339387</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1619140639516411</v>
+      </c>
+      <c r="C49">
+        <v>-35.35965561720472</v>
+      </c>
+      <c r="D49">
+        <v>30.6613443827953</v>
+      </c>
+      <c r="E49">
+        <v>3.946000000000012</v>
+      </c>
+      <c r="F49">
+        <v>66.64600000000002</v>
+      </c>
+      <c r="G49">
+        <v>0.625</v>
+      </c>
+      <c r="H49">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>-1.69</v>
+      </c>
+      <c r="L49">
+        <v>1.69</v>
+      </c>
+      <c r="M49">
+        <v>15.91506480000001</v>
+      </c>
+      <c r="N49">
+        <v>-14.22506480000001</v>
+      </c>
+      <c r="O49">
+        <v>-3.983018144</v>
+      </c>
+      <c r="P49">
+        <v>-10.242046656</v>
+      </c>
+      <c r="Q49">
+        <v>-11.932046656</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1000286008508224</v>
+      </c>
+      <c r="T49">
+        <v>1.035274145653435</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.02973283526938575</v>
+      </c>
+      <c r="W49">
+        <v>0.2316997989376707</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.1061886973906634</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1639140639516411</v>
+      </c>
+      <c r="C50">
+        <v>-37.267789874128</v>
+      </c>
+      <c r="D50">
+        <v>30.17121012587201</v>
+      </c>
+      <c r="E50">
+        <v>5.364000000000004</v>
+      </c>
+      <c r="F50">
+        <v>68.06400000000001</v>
+      </c>
+      <c r="G50">
+        <v>0.625</v>
+      </c>
+      <c r="H50">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>-1.69</v>
+      </c>
+      <c r="L50">
+        <v>1.69</v>
+      </c>
+      <c r="M50">
+        <v>16.2536832</v>
+      </c>
+      <c r="N50">
+        <v>-14.5636832</v>
+      </c>
+      <c r="O50">
+        <v>-4.077831295999999</v>
+      </c>
+      <c r="P50">
+        <v>-10.485851904</v>
+      </c>
+      <c r="Q50">
+        <v>-12.175851904</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1012060739441075</v>
+      </c>
+      <c r="T50">
+        <v>1.055183263839078</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.02911340120127355</v>
+      </c>
+      <c r="W50">
+        <v>0.2318477197931359</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.1039764328616912</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1659140639516411</v>
+      </c>
+      <c r="C51">
+        <v>-39.16050068405615</v>
+      </c>
+      <c r="D51">
+        <v>29.69649931594385</v>
+      </c>
+      <c r="E51">
+        <v>6.781999999999996</v>
+      </c>
+      <c r="F51">
+        <v>69.482</v>
+      </c>
+      <c r="G51">
+        <v>0.625</v>
+      </c>
+      <c r="H51">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>-1.69</v>
+      </c>
+      <c r="L51">
+        <v>1.69</v>
+      </c>
+      <c r="M51">
+        <v>16.5923016</v>
+      </c>
+      <c r="N51">
+        <v>-14.9023016</v>
+      </c>
+      <c r="O51">
+        <v>-4.172644447999999</v>
+      </c>
+      <c r="P51">
+        <v>-10.729657152</v>
+      </c>
+      <c r="Q51">
+        <v>-12.419657152</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1024297224528155</v>
+      </c>
+      <c r="T51">
+        <v>1.075873131757491</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.02851925015634961</v>
+      </c>
+      <c r="W51">
+        <v>0.2319896030626637</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.1018544648441058</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1679140639516411</v>
+      </c>
+      <c r="C52">
+        <v>-41.03850478286705</v>
+      </c>
+      <c r="D52">
+        <v>29.23649521713295</v>
+      </c>
+      <c r="E52">
+        <v>8.200000000000003</v>
+      </c>
+      <c r="F52">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="G52">
+        <v>0.625</v>
+      </c>
+      <c r="H52">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>-1.69</v>
+      </c>
+      <c r="L52">
+        <v>1.69</v>
+      </c>
+      <c r="M52">
+        <v>16.93092</v>
+      </c>
+      <c r="N52">
+        <v>-15.24092</v>
+      </c>
+      <c r="O52">
+        <v>-4.2674576</v>
+      </c>
+      <c r="P52">
+        <v>-10.9734624</v>
+      </c>
+      <c r="Q52">
+        <v>-12.6634624</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1037023169018717</v>
+      </c>
+      <c r="T52">
+        <v>1.097390594392641</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.02794886515322261</v>
+      </c>
+      <c r="W52">
+        <v>0.2321258110014105</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.09981737554722359</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1699140639516411</v>
+      </c>
+      <c r="C53">
+        <v>-42.90247517438686</v>
+      </c>
+      <c r="D53">
+        <v>28.79052482561315</v>
+      </c>
+      <c r="E53">
+        <v>9.618000000000009</v>
+      </c>
+      <c r="F53">
+        <v>72.31800000000001</v>
+      </c>
+      <c r="G53">
+        <v>0.625</v>
+      </c>
+      <c r="H53">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>-1.69</v>
+      </c>
+      <c r="L53">
+        <v>1.69</v>
+      </c>
+      <c r="M53">
+        <v>17.26953840000001</v>
+      </c>
+      <c r="N53">
+        <v>-15.57953840000001</v>
+      </c>
+      <c r="O53">
+        <v>-4.362270752000001</v>
+      </c>
+      <c r="P53">
+        <v>-11.21726764800001</v>
+      </c>
+      <c r="Q53">
+        <v>-12.907267648</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1050268539815018</v>
+      </c>
+      <c r="T53">
+        <v>1.119786320808817</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.02740084818943393</v>
+      </c>
+      <c r="W53">
+        <v>0.2322566774523632</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.09786017210512121</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1719140639516411</v>
+      </c>
+      <c r="C54">
+        <v>-44.75304441569666</v>
+      </c>
+      <c r="D54">
+        <v>28.35795558430335</v>
+      </c>
+      <c r="E54">
+        <v>11.036</v>
+      </c>
+      <c r="F54">
+        <v>73.736</v>
+      </c>
+      <c r="G54">
+        <v>0.625</v>
+      </c>
+      <c r="H54">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>-1.69</v>
+      </c>
+      <c r="L54">
+        <v>1.69</v>
+      </c>
+      <c r="M54">
+        <v>17.6081568</v>
+      </c>
+      <c r="N54">
+        <v>-15.9181568</v>
+      </c>
+      <c r="O54">
+        <v>-4.457083904</v>
+      </c>
+      <c r="P54">
+        <v>-11.461072896</v>
+      </c>
+      <c r="Q54">
+        <v>-13.151072896</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1064065801061164</v>
+      </c>
+      <c r="T54">
+        <v>1.143115202492334</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.02687390880117559</v>
+      </c>
+      <c r="W54">
+        <v>0.2323825105782793</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.09597824571848423</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1739140639516411</v>
+      </c>
+      <c r="C55">
+        <v>-46.59080761065842</v>
+      </c>
+      <c r="D55">
+        <v>27.93819238934159</v>
+      </c>
+      <c r="E55">
+        <v>12.45400000000001</v>
+      </c>
+      <c r="F55">
+        <v>75.15400000000001</v>
+      </c>
+      <c r="G55">
+        <v>0.625</v>
+      </c>
+      <c r="H55">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>-1.69</v>
+      </c>
+      <c r="L55">
+        <v>1.69</v>
+      </c>
+      <c r="M55">
+        <v>17.9467752</v>
+      </c>
+      <c r="N55">
+        <v>-16.2567752</v>
+      </c>
+      <c r="O55">
+        <v>-4.551897056</v>
+      </c>
+      <c r="P55">
+        <v>-11.704878144</v>
+      </c>
+      <c r="Q55">
+        <v>-13.394878144</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1078450179807146</v>
+      </c>
+      <c r="T55">
+        <v>1.167436802545363</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.02636685391813454</v>
+      </c>
+      <c r="W55">
+        <v>0.2325035952843495</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.09416733542190914</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1759140639516411</v>
+      </c>
+      <c r="C56">
+        <v>-48.41632514145228</v>
+      </c>
+      <c r="D56">
+        <v>27.53067485854774</v>
+      </c>
+      <c r="E56">
+        <v>13.87200000000001</v>
+      </c>
+      <c r="F56">
+        <v>76.57200000000002</v>
+      </c>
+      <c r="G56">
+        <v>0.625</v>
+      </c>
+      <c r="H56">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>-1.69</v>
+      </c>
+      <c r="L56">
+        <v>1.69</v>
+      </c>
+      <c r="M56">
+        <v>18.28539360000001</v>
+      </c>
+      <c r="N56">
+        <v>-16.5953936</v>
+      </c>
+      <c r="O56">
+        <v>-4.646710208</v>
+      </c>
+      <c r="P56">
+        <v>-11.948683392</v>
+      </c>
+      <c r="Q56">
+        <v>-13.638683392</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1093459966324693</v>
+      </c>
+      <c r="T56">
+        <v>1.192815863470262</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.02587857884557649</v>
+      </c>
+      <c r="W56">
+        <v>0.2326201953716763</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.092423495877059</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1779140639516411</v>
+      </c>
+      <c r="C57">
+        <v>-50.23012516449117</v>
+      </c>
+      <c r="D57">
+        <v>27.13487483550884</v>
+      </c>
+      <c r="E57">
+        <v>15.29000000000001</v>
+      </c>
+      <c r="F57">
+        <v>77.99000000000001</v>
+      </c>
+      <c r="G57">
+        <v>0.625</v>
+      </c>
+      <c r="H57">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>-1.69</v>
+      </c>
+      <c r="L57">
+        <v>1.69</v>
+      </c>
+      <c r="M57">
+        <v>18.624012</v>
+      </c>
+      <c r="N57">
+        <v>-16.934012</v>
+      </c>
+      <c r="O57">
+        <v>-4.74152336</v>
+      </c>
+      <c r="P57">
+        <v>-12.19248864</v>
+      </c>
+      <c r="Q57">
+        <v>-13.88248864</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1109136854465242</v>
+      </c>
+      <c r="T57">
+        <v>1.21932288265849</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.02540805923020237</v>
+      </c>
+      <c r="W57">
+        <v>0.2327325554558277</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.09074306867929427</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1799140639516411</v>
+      </c>
+      <c r="C58">
+        <v>-52.03270589408888</v>
+      </c>
+      <c r="D58">
+        <v>26.75029410591114</v>
+      </c>
+      <c r="E58">
+        <v>16.70800000000001</v>
+      </c>
+      <c r="F58">
+        <v>79.40800000000002</v>
+      </c>
+      <c r="G58">
+        <v>0.625</v>
+      </c>
+      <c r="H58">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>-1.69</v>
+      </c>
+      <c r="L58">
+        <v>1.69</v>
+      </c>
+      <c r="M58">
+        <v>18.96263040000001</v>
+      </c>
+      <c r="N58">
+        <v>-17.2726304</v>
+      </c>
+      <c r="O58">
+        <v>-4.836336512</v>
+      </c>
+      <c r="P58">
+        <v>-12.43629388800001</v>
+      </c>
+      <c r="Q58">
+        <v>-14.126293888</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1125526328430361</v>
+      </c>
+      <c r="T58">
+        <v>1.247034766355273</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.0249543438868059</v>
+      </c>
+      <c r="W58">
+        <v>0.2328409026798308</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.08912265673859254</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1819140639516411</v>
+      </c>
+      <c r="C59">
+        <v>-53.82453769464415</v>
+      </c>
+      <c r="D59">
+        <v>26.37646230535587</v>
+      </c>
+      <c r="E59">
+        <v>18.12600000000002</v>
+      </c>
+      <c r="F59">
+        <v>80.82600000000002</v>
+      </c>
+      <c r="G59">
+        <v>0.625</v>
+      </c>
+      <c r="H59">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>-1.69</v>
+      </c>
+      <c r="L59">
+        <v>1.69</v>
+      </c>
+      <c r="M59">
+        <v>19.30124880000001</v>
+      </c>
+      <c r="N59">
+        <v>-17.61124880000001</v>
+      </c>
+      <c r="O59">
+        <v>-4.931149664</v>
+      </c>
+      <c r="P59">
+        <v>-12.68009913600001</v>
+      </c>
+      <c r="Q59">
+        <v>-14.37009913600001</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1142678103510137</v>
+      </c>
+      <c r="T59">
+        <v>1.276035574875164</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.02451654838001983</v>
+      </c>
+      <c r="W59">
+        <v>0.2329454482468513</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.08755910135721379</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1839140639516411</v>
+      </c>
+      <c r="C60">
+        <v>-55.60606499981483</v>
+      </c>
+      <c r="D60">
+        <v>26.01293500018517</v>
+      </c>
+      <c r="E60">
+        <v>19.544</v>
+      </c>
+      <c r="F60">
+        <v>82.244</v>
+      </c>
+      <c r="G60">
+        <v>0.625</v>
+      </c>
+      <c r="H60">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>-1.69</v>
+      </c>
+      <c r="L60">
+        <v>1.69</v>
+      </c>
+      <c r="M60">
+        <v>19.6398672</v>
+      </c>
+      <c r="N60">
+        <v>-17.9498672</v>
+      </c>
+      <c r="O60">
+        <v>-5.025962815999998</v>
+      </c>
+      <c r="P60">
+        <v>-12.923904384</v>
+      </c>
+      <c r="Q60">
+        <v>-14.613904384</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1160646629784187</v>
+      </c>
+      <c r="T60">
+        <v>1.306417374276953</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.0240938492700195</v>
+      </c>
+      <c r="W60">
+        <v>0.2330463887943194</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.08604946167864114</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1859140639516411</v>
+      </c>
+      <c r="C61">
+        <v>-57.37770807514632</v>
+      </c>
+      <c r="D61">
+        <v>25.65929192485369</v>
+      </c>
+      <c r="E61">
+        <v>20.962</v>
+      </c>
+      <c r="F61">
+        <v>83.66200000000001</v>
+      </c>
+      <c r="G61">
+        <v>0.625</v>
+      </c>
+      <c r="H61">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>-1.69</v>
+      </c>
+      <c r="L61">
+        <v>1.69</v>
+      </c>
+      <c r="M61">
+        <v>19.9784856</v>
+      </c>
+      <c r="N61">
+        <v>-18.2884856</v>
+      </c>
+      <c r="O61">
+        <v>-5.120775967999998</v>
+      </c>
+      <c r="P61">
+        <v>-13.167709632</v>
+      </c>
+      <c r="Q61">
+        <v>-14.857709632</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1179491669535021</v>
+      </c>
+      <c r="T61">
+        <v>1.338281212673952</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.02368547894340899</v>
+      </c>
+      <c r="W61">
+        <v>0.2331439076283139</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.08459099622646082</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1879140639516411</v>
+      </c>
+      <c r="C62">
+        <v>-59.13986463885148</v>
+      </c>
+      <c r="D62">
+        <v>25.31513536114852</v>
+      </c>
+      <c r="E62">
+        <v>22.38</v>
+      </c>
+      <c r="F62">
+        <v>85.08</v>
+      </c>
+      <c r="G62">
+        <v>0.625</v>
+      </c>
+      <c r="H62">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>-1.69</v>
+      </c>
+      <c r="L62">
+        <v>1.69</v>
+      </c>
+      <c r="M62">
+        <v>20.317104</v>
+      </c>
+      <c r="N62">
+        <v>-18.627104</v>
+      </c>
+      <c r="O62">
+        <v>-5.215589119999998</v>
+      </c>
+      <c r="P62">
+        <v>-13.41151488</v>
+      </c>
+      <c r="Q62">
+        <v>-15.10151488</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1199278961273397</v>
+      </c>
+      <c r="T62">
+        <v>1.371738242990801</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.02329072096101885</v>
+      </c>
+      <c r="W62">
+        <v>0.2332381758345087</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.08318114628935314</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1899140639516411</v>
+      </c>
+      <c r="C63">
+        <v>-60.89291135388457</v>
+      </c>
+      <c r="D63">
+        <v>24.98008864611543</v>
+      </c>
+      <c r="E63">
+        <v>23.798</v>
+      </c>
+      <c r="F63">
+        <v>86.498</v>
+      </c>
+      <c r="G63">
+        <v>0.625</v>
+      </c>
+      <c r="H63">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>-1.69</v>
+      </c>
+      <c r="L63">
+        <v>1.69</v>
+      </c>
+      <c r="M63">
+        <v>20.6557224</v>
+      </c>
+      <c r="N63">
+        <v>-18.9657224</v>
+      </c>
+      <c r="O63">
+        <v>-5.310402271999998</v>
+      </c>
+      <c r="P63">
+        <v>-13.655320128</v>
+      </c>
+      <c r="Q63">
+        <v>-15.345320128</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1220080985921433</v>
+      </c>
+      <c r="T63">
+        <v>1.406911018452103</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.02290890586329722</v>
+      </c>
+      <c r="W63">
+        <v>0.2333293532798446</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.08181752094034733</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1919140639516411</v>
+      </c>
+      <c r="C64">
+        <v>-62.63720520307669</v>
+      </c>
+      <c r="D64">
+        <v>24.65379479692333</v>
+      </c>
+      <c r="E64">
+        <v>25.21600000000001</v>
+      </c>
+      <c r="F64">
+        <v>87.91600000000001</v>
+      </c>
+      <c r="G64">
+        <v>0.625</v>
+      </c>
+      <c r="H64">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>-1.69</v>
+      </c>
+      <c r="L64">
+        <v>1.69</v>
+      </c>
+      <c r="M64">
+        <v>20.9943408</v>
+      </c>
+      <c r="N64">
+        <v>-19.3043408</v>
+      </c>
+      <c r="O64">
+        <v>-5.405215423999999</v>
+      </c>
+      <c r="P64">
+        <v>-13.899125376</v>
+      </c>
+      <c r="Q64">
+        <v>-15.589125376</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1241977853971997</v>
+      </c>
+      <c r="T64">
+        <v>1.443934992621895</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.02253940738163114</v>
+      </c>
+      <c r="W64">
+        <v>0.2334175895172665</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.08049788350582554</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1939140639516411</v>
+      </c>
+      <c r="C65">
+        <v>-64.37308475788751</v>
+      </c>
+      <c r="D65">
+        <v>24.33591524211248</v>
+      </c>
+      <c r="E65">
+        <v>26.634</v>
+      </c>
+      <c r="F65">
+        <v>89.334</v>
+      </c>
+      <c r="G65">
+        <v>0.625</v>
+      </c>
+      <c r="H65">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>-1.69</v>
+      </c>
+      <c r="L65">
+        <v>1.69</v>
+      </c>
+      <c r="M65">
+        <v>21.3329592</v>
+      </c>
+      <c r="N65">
+        <v>-19.6429592</v>
+      </c>
+      <c r="O65">
+        <v>-5.500028575999998</v>
+      </c>
+      <c r="P65">
+        <v>-14.142930624</v>
+      </c>
+      <c r="Q65">
+        <v>-15.832930624</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1265058336511781</v>
+      </c>
+      <c r="T65">
+        <v>1.482960262692758</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.02218163901049414</v>
+      </c>
+      <c r="W65">
+        <v>0.233503024604294</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.07922013932319338</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1959140639516411</v>
+      </c>
+      <c r="C66">
+        <v>-66.10087135025272</v>
+      </c>
+      <c r="D66">
+        <v>24.0261286497473</v>
+      </c>
+      <c r="E66">
+        <v>28.05200000000001</v>
+      </c>
+      <c r="F66">
+        <v>90.75200000000001</v>
+      </c>
+      <c r="G66">
+        <v>0.625</v>
+      </c>
+      <c r="H66">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>-1.69</v>
+      </c>
+      <c r="L66">
+        <v>1.69</v>
+      </c>
+      <c r="M66">
+        <v>21.6715776</v>
+      </c>
+      <c r="N66">
+        <v>-19.9815776</v>
+      </c>
+      <c r="O66">
+        <v>-5.594841727999999</v>
+      </c>
+      <c r="P66">
+        <v>-14.386735872</v>
+      </c>
+      <c r="Q66">
+        <v>-16.076735872</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1289421068081552</v>
+      </c>
+      <c r="T66">
+        <v>1.524153603323112</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.02183505090095517</v>
+      </c>
+      <c r="W66">
+        <v>0.2335857898448519</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.07798232464626853</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1979140639516411</v>
+      </c>
+      <c r="C67">
+        <v>-67.82087015605345</v>
+      </c>
+      <c r="D67">
+        <v>23.72412984394657</v>
+      </c>
+      <c r="E67">
+        <v>29.47000000000001</v>
+      </c>
+      <c r="F67">
+        <v>92.17000000000002</v>
+      </c>
+      <c r="G67">
+        <v>0.625</v>
+      </c>
+      <c r="H67">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>-1.69</v>
+      </c>
+      <c r="L67">
+        <v>1.69</v>
+      </c>
+      <c r="M67">
+        <v>22.010196</v>
+      </c>
+      <c r="N67">
+        <v>-20.320196</v>
+      </c>
+      <c r="O67">
+        <v>-5.689654879999999</v>
+      </c>
+      <c r="P67">
+        <v>-14.63054112</v>
+      </c>
+      <c r="Q67">
+        <v>-16.32054112000001</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1315175955741025</v>
+      </c>
+      <c r="T67">
+        <v>1.567700849132344</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.02149912704094047</v>
+      </c>
+      <c r="W67">
+        <v>0.2336660084626234</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.07678259657478748</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1999140639516411</v>
+      </c>
+      <c r="C68">
+        <v>-69.53337119788759</v>
+      </c>
+      <c r="D68">
+        <v>23.42962880211241</v>
+      </c>
+      <c r="E68">
+        <v>30.88800000000001</v>
+      </c>
+      <c r="F68">
+        <v>93.58800000000001</v>
+      </c>
+      <c r="G68">
+        <v>0.625</v>
+      </c>
+      <c r="H68">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>-1.69</v>
+      </c>
+      <c r="L68">
+        <v>1.69</v>
+      </c>
+      <c r="M68">
+        <v>22.3488144</v>
+      </c>
+      <c r="N68">
+        <v>-20.6588144</v>
+      </c>
+      <c r="O68">
+        <v>-5.784468031999999</v>
+      </c>
+      <c r="P68">
+        <v>-14.874346368</v>
+      </c>
+      <c r="Q68">
+        <v>-16.564346368</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1342445836792232</v>
+      </c>
+      <c r="T68">
+        <v>1.613809697636236</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.02117338269183531</v>
+      </c>
+      <c r="W68">
+        <v>0.2337437962131897</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.07561922389941189</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2019140639516411</v>
+      </c>
+      <c r="C69">
+        <v>-71.23865027406902</v>
+      </c>
+      <c r="D69">
+        <v>23.142349725931</v>
+      </c>
+      <c r="E69">
+        <v>32.30600000000001</v>
+      </c>
+      <c r="F69">
+        <v>95.00600000000001</v>
+      </c>
+      <c r="G69">
+        <v>0.625</v>
+      </c>
+      <c r="H69">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>-1.69</v>
+      </c>
+      <c r="L69">
+        <v>1.69</v>
+      </c>
+      <c r="M69">
+        <v>22.6874328</v>
+      </c>
+      <c r="N69">
+        <v>-20.9974328</v>
+      </c>
+      <c r="O69">
+        <v>-5.879281183999999</v>
+      </c>
+      <c r="P69">
+        <v>-15.118151616</v>
+      </c>
+      <c r="Q69">
+        <v>-16.808151616</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1371368437907148</v>
+      </c>
+      <c r="T69">
+        <v>1.662713021807031</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.02085736205464374</v>
+      </c>
+      <c r="W69">
+        <v>0.2338192619413511</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.07449057876658483</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2039140639516411</v>
+      </c>
+      <c r="C70">
+        <v>-72.93696982010975</v>
+      </c>
+      <c r="D70">
+        <v>22.86203017989027</v>
+      </c>
+      <c r="E70">
+        <v>33.72400000000002</v>
+      </c>
+      <c r="F70">
+        <v>96.42400000000002</v>
+      </c>
+      <c r="G70">
+        <v>0.625</v>
+      </c>
+      <c r="H70">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>-1.69</v>
+      </c>
+      <c r="L70">
+        <v>1.69</v>
+      </c>
+      <c r="M70">
+        <v>23.0260512</v>
+      </c>
+      <c r="N70">
+        <v>-21.3360512</v>
+      </c>
+      <c r="O70">
+        <v>-5.974094335999999</v>
+      </c>
+      <c r="P70">
+        <v>-15.361956864</v>
+      </c>
+      <c r="Q70">
+        <v>-17.051956864</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1402098701591746</v>
+      </c>
+      <c r="T70">
+        <v>1.714672803738502</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.02055063614207545</v>
+      </c>
+      <c r="W70">
+        <v>0.2338925080892724</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.07339512907884094</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2059140639516411</v>
+      </c>
+      <c r="C71">
+        <v>-74.62857970834159</v>
+      </c>
+      <c r="D71">
+        <v>22.58842029165842</v>
+      </c>
+      <c r="E71">
+        <v>35.14200000000001</v>
+      </c>
+      <c r="F71">
+        <v>97.84200000000001</v>
+      </c>
+      <c r="G71">
+        <v>0.625</v>
+      </c>
+      <c r="H71">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>-1.69</v>
+      </c>
+      <c r="L71">
+        <v>1.69</v>
+      </c>
+      <c r="M71">
+        <v>23.3646696</v>
+      </c>
+      <c r="N71">
+        <v>-21.6746696</v>
+      </c>
+      <c r="O71">
+        <v>-6.068907487999999</v>
+      </c>
+      <c r="P71">
+        <v>-15.605762112</v>
+      </c>
+      <c r="Q71">
+        <v>-17.295762112</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1434811562933416</v>
+      </c>
+      <c r="T71">
+        <v>1.76998482966555</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.02025280083566856</v>
+      </c>
+      <c r="W71">
+        <v>0.2339636311604424</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.07233143155595922</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2079140639516411</v>
+      </c>
+      <c r="C72">
+        <v>-76.31371799079832</v>
+      </c>
+      <c r="D72">
+        <v>22.3212820092017</v>
+      </c>
+      <c r="E72">
+        <v>36.56000000000002</v>
+      </c>
+      <c r="F72">
+        <v>99.26000000000002</v>
+      </c>
+      <c r="G72">
+        <v>0.625</v>
+      </c>
+      <c r="H72">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <v>-1.69</v>
+      </c>
+      <c r="L72">
+        <v>1.69</v>
+      </c>
+      <c r="M72">
+        <v>23.703288</v>
+      </c>
+      <c r="N72">
+        <v>-22.013288</v>
+      </c>
+      <c r="O72">
+        <v>-6.163720639999999</v>
+      </c>
+      <c r="P72">
+        <v>-15.84956736</v>
+      </c>
+      <c r="Q72">
+        <v>-17.53956736</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1469705281697863</v>
+      </c>
+      <c r="T72">
+        <v>1.828984323987735</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.01996347510944472</v>
+      </c>
+      <c r="W72">
+        <v>0.2340327221438646</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.0712981253908741</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2099140639516411</v>
+      </c>
+      <c r="C73">
+        <v>-77.99261159000017</v>
+      </c>
+      <c r="D73">
+        <v>22.06038840999982</v>
+      </c>
+      <c r="E73">
+        <v>37.97799999999999</v>
+      </c>
+      <c r="F73">
+        <v>100.678</v>
+      </c>
+      <c r="G73">
+        <v>0.625</v>
+      </c>
+      <c r="H73">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>-1.69</v>
+      </c>
+      <c r="L73">
+        <v>1.69</v>
+      </c>
+      <c r="M73">
+        <v>24.0419064</v>
+      </c>
+      <c r="N73">
+        <v>-22.3519064</v>
+      </c>
+      <c r="O73">
+        <v>-6.258533791999998</v>
+      </c>
+      <c r="P73">
+        <v>-16.093372608</v>
+      </c>
+      <c r="Q73">
+        <v>-17.783372608</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1507005463825375</v>
+      </c>
+      <c r="T73">
+        <v>1.892052748952828</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.01968229940367789</v>
+      </c>
+      <c r="W73">
+        <v>0.2340998669024017</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.07029392644170684</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2119140639516411</v>
+      </c>
+      <c r="C74">
+        <v>-79.66547694185469</v>
+      </c>
+      <c r="D74">
+        <v>21.80552305814531</v>
+      </c>
+      <c r="E74">
+        <v>39.396</v>
+      </c>
+      <c r="F74">
+        <v>102.096</v>
+      </c>
+      <c r="G74">
+        <v>0.625</v>
+      </c>
+      <c r="H74">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <v>-1.69</v>
+      </c>
+      <c r="L74">
+        <v>1.69</v>
+      </c>
+      <c r="M74">
+        <v>24.3805248</v>
+      </c>
+      <c r="N74">
+        <v>-22.6905248</v>
+      </c>
+      <c r="O74">
+        <v>-6.353346943999998</v>
+      </c>
+      <c r="P74">
+        <v>-16.337177856</v>
+      </c>
+      <c r="Q74">
+        <v>-18.02717785600001</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1546969944676281</v>
+      </c>
+      <c r="T74">
+        <v>1.95962606141543</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.01940893413418237</v>
+      </c>
+      <c r="W74">
+        <v>0.2341651465287573</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.06931762190779422</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2139140639516411</v>
+      </c>
+      <c r="C75">
+        <v>-81.3325205945012</v>
+      </c>
+      <c r="D75">
+        <v>21.55647940549881</v>
+      </c>
+      <c r="E75">
+        <v>40.81400000000001</v>
+      </c>
+      <c r="F75">
+        <v>103.514</v>
+      </c>
+      <c r="G75">
+        <v>0.625</v>
+      </c>
+      <c r="H75">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>-1.69</v>
+      </c>
+      <c r="L75">
+        <v>1.69</v>
+      </c>
+      <c r="M75">
+        <v>24.7191432</v>
+      </c>
+      <c r="N75">
+        <v>-23.0291432</v>
+      </c>
+      <c r="O75">
+        <v>-6.448160095999999</v>
+      </c>
+      <c r="P75">
+        <v>-16.580983104</v>
+      </c>
+      <c r="Q75">
+        <v>-18.27098310400001</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.158989475744207</v>
+      </c>
+      <c r="T75">
+        <v>2.032204804430816</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.01914305832412507</v>
+      </c>
+      <c r="W75">
+        <v>0.2342286376721989</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.06836806544330387</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2159140639516411</v>
+      </c>
+      <c r="C76">
+        <v>-82.99393976658213</v>
+      </c>
+      <c r="D76">
+        <v>21.31306023341787</v>
+      </c>
+      <c r="E76">
+        <v>42.232</v>
+      </c>
+      <c r="F76">
+        <v>104.932</v>
+      </c>
+      <c r="G76">
+        <v>0.625</v>
+      </c>
+      <c r="H76">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>-1.69</v>
+      </c>
+      <c r="L76">
+        <v>1.69</v>
+      </c>
+      <c r="M76">
+        <v>25.0577616</v>
+      </c>
+      <c r="N76">
+        <v>-23.3677616</v>
+      </c>
+      <c r="O76">
+        <v>-6.542973247999998</v>
+      </c>
+      <c r="P76">
+        <v>-16.824788352</v>
+      </c>
+      <c r="Q76">
+        <v>-18.514788352</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.1636121478882149</v>
+      </c>
+      <c r="T76">
+        <v>2.110366527678155</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.01888436834677203</v>
+      </c>
+      <c r="W76">
+        <v>0.2342904128387909</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.06744417266704306</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2179140639516411</v>
+      </c>
+      <c r="C77">
+        <v>-84.64992286811203</v>
+      </c>
+      <c r="D77">
+        <v>21.07507713188798</v>
+      </c>
+      <c r="E77">
+        <v>43.65000000000001</v>
+      </c>
+      <c r="F77">
+        <v>106.35</v>
+      </c>
+      <c r="G77">
+        <v>0.625</v>
+      </c>
+      <c r="H77">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>-1.69</v>
+      </c>
+      <c r="L77">
+        <v>1.69</v>
+      </c>
+      <c r="M77">
+        <v>25.39638</v>
+      </c>
+      <c r="N77">
+        <v>-23.70638</v>
+      </c>
+      <c r="O77">
+        <v>-6.637786399999999</v>
+      </c>
+      <c r="P77">
+        <v>-17.0685936</v>
+      </c>
+      <c r="Q77">
+        <v>-18.7585936</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.1686046338037435</v>
+      </c>
+      <c r="T77">
+        <v>2.194781188785282</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.01863257676881507</v>
+      </c>
+      <c r="W77">
+        <v>0.234350540667607</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.06654491703148246</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2199140639516411</v>
+      </c>
+      <c r="C78">
+        <v>-86.30064998683558</v>
+      </c>
+      <c r="D78">
+        <v>20.84235001316444</v>
+      </c>
+      <c r="E78">
+        <v>45.06800000000001</v>
+      </c>
+      <c r="F78">
+        <v>107.768</v>
+      </c>
+      <c r="G78">
+        <v>0.625</v>
+      </c>
+      <c r="H78">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>-1.69</v>
+      </c>
+      <c r="L78">
+        <v>1.69</v>
+      </c>
+      <c r="M78">
+        <v>25.73499840000001</v>
+      </c>
+      <c r="N78">
+        <v>-24.0449984</v>
+      </c>
+      <c r="O78">
+        <v>-6.732599551999999</v>
+      </c>
+      <c r="P78">
+        <v>-17.312398848</v>
+      </c>
+      <c r="Q78">
+        <v>-19.00239884800001</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.1740131602122329</v>
+      </c>
+      <c r="T78">
+        <v>2.286230404984669</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.01838741128501488</v>
+      </c>
+      <c r="W78">
+        <v>0.2344090861851384</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.06566932601791031</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2219140639516411</v>
+      </c>
+      <c r="C79">
+        <v>-87.94629334271312</v>
+      </c>
+      <c r="D79">
+        <v>20.61470665728688</v>
+      </c>
+      <c r="E79">
+        <v>46.486</v>
+      </c>
+      <c r="F79">
+        <v>109.186</v>
+      </c>
+      <c r="G79">
+        <v>0.625</v>
+      </c>
+      <c r="H79">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <v>-1.69</v>
+      </c>
+      <c r="L79">
+        <v>1.69</v>
+      </c>
+      <c r="M79">
+        <v>26.0736168</v>
+      </c>
+      <c r="N79">
+        <v>-24.3836168</v>
+      </c>
+      <c r="O79">
+        <v>-6.827412703999999</v>
+      </c>
+      <c r="P79">
+        <v>-17.556204096</v>
+      </c>
+      <c r="Q79">
+        <v>-19.246204096</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.1798919932649386</v>
+      </c>
+      <c r="T79">
+        <v>2.385631726940523</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.01814861373585884</v>
+      </c>
+      <c r="W79">
+        <v>0.2344661110398769</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.0648164776280673</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2239140639516411</v>
+      </c>
+      <c r="C80">
+        <v>-89.58701771294436</v>
+      </c>
+      <c r="D80">
+        <v>20.39198228705566</v>
+      </c>
+      <c r="E80">
+        <v>47.90400000000001</v>
+      </c>
+      <c r="F80">
+        <v>110.604</v>
+      </c>
+      <c r="G80">
+        <v>0.625</v>
+      </c>
+      <c r="H80">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <v>-1.69</v>
+      </c>
+      <c r="L80">
+        <v>1.69</v>
+      </c>
+      <c r="M80">
+        <v>26.4122352</v>
+      </c>
+      <c r="N80">
+        <v>-24.7222352</v>
+      </c>
+      <c r="O80">
+        <v>-6.922225855999999</v>
+      </c>
+      <c r="P80">
+        <v>-17.800009344</v>
+      </c>
+      <c r="Q80">
+        <v>-19.490009344</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.1863052656860722</v>
+      </c>
+      <c r="T80">
+        <v>2.494069532710547</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.01791593920078373</v>
+      </c>
+      <c r="W80">
+        <v>0.2345216737188529</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.06398549714565627</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2259140639516411</v>
+      </c>
+      <c r="C81">
+        <v>-91.2229808297342</v>
+      </c>
+      <c r="D81">
+        <v>20.17401917026582</v>
+      </c>
+      <c r="E81">
+        <v>49.32200000000002</v>
+      </c>
+      <c r="F81">
+        <v>112.022</v>
+      </c>
+      <c r="G81">
+        <v>0.625</v>
+      </c>
+      <c r="H81">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0</v>
+      </c>
+      <c r="K81">
+        <v>-1.69</v>
+      </c>
+      <c r="L81">
+        <v>1.69</v>
+      </c>
+      <c r="M81">
+        <v>26.75085360000001</v>
+      </c>
+      <c r="N81">
+        <v>-25.06085360000001</v>
+      </c>
+      <c r="O81">
+        <v>-7.017039007999999</v>
+      </c>
+      <c r="P81">
+        <v>-18.043814592</v>
+      </c>
+      <c r="Q81">
+        <v>-19.73381459200001</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.1933293259568375</v>
+      </c>
+      <c r="T81">
+        <v>2.612834748553907</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.01768915516026747</v>
+      </c>
+      <c r="W81">
+        <v>0.2345758297477281</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.06317555414381248</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2279140639516411</v>
+      </c>
+      <c r="C82">
+        <v>-92.854333752819</v>
+      </c>
+      <c r="D82">
+        <v>19.96066624718101</v>
+      </c>
+      <c r="E82">
+        <v>50.74000000000001</v>
+      </c>
+      <c r="F82">
+        <v>113.44</v>
+      </c>
+      <c r="G82">
+        <v>0.625</v>
+      </c>
+      <c r="H82">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <v>-1.69</v>
+      </c>
+      <c r="L82">
+        <v>1.69</v>
+      </c>
+      <c r="M82">
+        <v>27.089472</v>
+      </c>
+      <c r="N82">
+        <v>-25.399472</v>
+      </c>
+      <c r="O82">
+        <v>-7.111852159999999</v>
+      </c>
+      <c r="P82">
+        <v>-18.28761984</v>
+      </c>
+      <c r="Q82">
+        <v>-19.97761984000001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2010557922546794</v>
+      </c>
+      <c r="T82">
+        <v>2.743476485981602</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.01746804072076413</v>
+      </c>
+      <c r="W82">
+        <v>0.2346286318758815</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.06238585971701482</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2299140639516411</v>
+      </c>
+      <c r="C83">
+        <v>-94.48122121860209</v>
+      </c>
+      <c r="D83">
+        <v>19.75177878139793</v>
+      </c>
+      <c r="E83">
+        <v>52.15800000000002</v>
+      </c>
+      <c r="F83">
+        <v>114.858</v>
+      </c>
+      <c r="G83">
+        <v>0.625</v>
+      </c>
+      <c r="H83">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83">
+        <v>-1.69</v>
+      </c>
+      <c r="L83">
+        <v>1.69</v>
+      </c>
+      <c r="M83">
+        <v>27.42809040000001</v>
+      </c>
+      <c r="N83">
+        <v>-25.7380904</v>
+      </c>
+      <c r="O83">
+        <v>-7.206665311999999</v>
+      </c>
+      <c r="P83">
+        <v>-18.53142508800001</v>
+      </c>
+      <c r="Q83">
+        <v>-20.22142508800001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2095955707943994</v>
+      </c>
+      <c r="T83">
+        <v>2.887869985243792</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.01725238589705099</v>
+      </c>
+      <c r="W83">
+        <v>0.2346801302477842</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.0616156639180393</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2319140639516411</v>
+      </c>
+      <c r="C84">
+        <v>-96.10378196759387</v>
+      </c>
+      <c r="D84">
+        <v>19.54721803240615</v>
+      </c>
+      <c r="E84">
+        <v>53.57600000000002</v>
+      </c>
+      <c r="F84">
+        <v>116.276</v>
+      </c>
+      <c r="G84">
+        <v>0.625</v>
+      </c>
+      <c r="H84">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <v>-1.69</v>
+      </c>
+      <c r="L84">
+        <v>1.69</v>
+      </c>
+      <c r="M84">
+        <v>27.76670880000001</v>
+      </c>
+      <c r="N84">
+        <v>-26.07670880000001</v>
+      </c>
+      <c r="O84">
+        <v>-7.301478464</v>
+      </c>
+      <c r="P84">
+        <v>-18.77523033600001</v>
+      </c>
+      <c r="Q84">
+        <v>-20.46523033600001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2190842136163105</v>
+      </c>
+      <c r="T84">
+        <v>3.048307206646225</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.01704199094708695</v>
+      </c>
+      <c r="W84">
+        <v>0.2347303725618357</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.06086425338245349</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2339140639516411</v>
+      </c>
+      <c r="C85">
+        <v>-97.72214905171397</v>
+      </c>
+      <c r="D85">
+        <v>19.34685094828605</v>
+      </c>
+      <c r="E85">
+        <v>54.99400000000001</v>
+      </c>
+      <c r="F85">
+        <v>117.694</v>
+      </c>
+      <c r="G85">
+        <v>0.625</v>
+      </c>
+      <c r="H85">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0</v>
+      </c>
+      <c r="K85">
+        <v>-1.69</v>
+      </c>
+      <c r="L85">
+        <v>1.69</v>
+      </c>
+      <c r="M85">
+        <v>28.1053272</v>
+      </c>
+      <c r="N85">
+        <v>-26.4153272</v>
+      </c>
+      <c r="O85">
+        <v>-7.396291615999999</v>
+      </c>
+      <c r="P85">
+        <v>-19.019035584</v>
+      </c>
+      <c r="Q85">
+        <v>-20.70903558400001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.2296891673584464</v>
+      </c>
+      <c r="T85">
+        <v>3.227619395272474</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.01683666575495338</v>
+      </c>
+      <c r="W85">
+        <v>0.2347794042177171</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.06013094912483352</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2359140639516411</v>
+      </c>
+      <c r="C86">
+        <v>-99.33645012288494</v>
+      </c>
+      <c r="D86">
+        <v>19.15054987711508</v>
+      </c>
+      <c r="E86">
+        <v>56.41200000000001</v>
+      </c>
+      <c r="F86">
+        <v>119.112</v>
+      </c>
+      <c r="G86">
+        <v>0.625</v>
+      </c>
+      <c r="H86">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <v>-1.69</v>
+      </c>
+      <c r="L86">
+        <v>1.69</v>
+      </c>
+      <c r="M86">
+        <v>28.4439456</v>
+      </c>
+      <c r="N86">
+        <v>-26.7539456</v>
+      </c>
+      <c r="O86">
+        <v>-7.491104767999998</v>
+      </c>
+      <c r="P86">
+        <v>-19.262840832</v>
+      </c>
+      <c r="Q86">
+        <v>-20.952840832</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.2416197403183492</v>
+      </c>
+      <c r="T86">
+        <v>3.429345607477002</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.0166362292578706</v>
+      </c>
+      <c r="W86">
+        <v>0.2348272684532205</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.05941510449239507</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2379140639516411</v>
+      </c>
+      <c r="C87">
+        <v>-100.9468077042335</v>
+      </c>
+      <c r="D87">
+        <v>18.95819229576647</v>
+      </c>
+      <c r="E87">
+        <v>57.83</v>
+      </c>
+      <c r="F87">
+        <v>120.53</v>
+      </c>
+      <c r="G87">
+        <v>0.625</v>
+      </c>
+      <c r="H87">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0</v>
+      </c>
+      <c r="K87">
+        <v>-1.69</v>
+      </c>
+      <c r="L87">
+        <v>1.69</v>
+      </c>
+      <c r="M87">
+        <v>28.782564</v>
+      </c>
+      <c r="N87">
+        <v>-27.092564</v>
+      </c>
+      <c r="O87">
+        <v>-7.585917919999997</v>
+      </c>
+      <c r="P87">
+        <v>-19.50664608</v>
+      </c>
+      <c r="Q87">
+        <v>-21.19664608</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.2551410563395725</v>
+      </c>
+      <c r="T87">
+        <v>3.657968647975469</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.01644050891366036</v>
+      </c>
+      <c r="W87">
+        <v>0.2348740064714179</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.05871610326307275</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2399140639516411</v>
+      </c>
+      <c r="C88">
+        <v>-102.55333944511</v>
+      </c>
+      <c r="D88">
+        <v>18.76966055489006</v>
+      </c>
+      <c r="E88">
+        <v>59.248</v>
+      </c>
+      <c r="F88">
+        <v>121.948</v>
+      </c>
+      <c r="G88">
+        <v>0.625</v>
+      </c>
+      <c r="H88">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0</v>
+      </c>
+      <c r="K88">
+        <v>-1.69</v>
+      </c>
+      <c r="L88">
+        <v>1.69</v>
+      </c>
+      <c r="M88">
+        <v>29.1211824</v>
+      </c>
+      <c r="N88">
+        <v>-27.4311824</v>
+      </c>
+      <c r="O88">
+        <v>-7.680731071999998</v>
+      </c>
+      <c r="P88">
+        <v>-19.750451328</v>
+      </c>
+      <c r="Q88">
+        <v>-21.44045132800001</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.2705939889352563</v>
+      </c>
+      <c r="T88">
+        <v>3.919252122830859</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.01624934020536199</v>
+      </c>
+      <c r="W88">
+        <v>0.2349196575589596</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.05803335787629282</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2419140639516411</v>
+      </c>
+      <c r="C89">
+        <v>-104.1561583610405</v>
+      </c>
+      <c r="D89">
+        <v>18.58484163895955</v>
+      </c>
+      <c r="E89">
+        <v>60.66600000000001</v>
+      </c>
+      <c r="F89">
+        <v>123.366</v>
+      </c>
+      <c r="G89">
+        <v>0.625</v>
+      </c>
+      <c r="H89">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0</v>
+      </c>
+      <c r="K89">
+        <v>-1.69</v>
+      </c>
+      <c r="L89">
+        <v>1.69</v>
+      </c>
+      <c r="M89">
+        <v>29.4598008</v>
+      </c>
+      <c r="N89">
+        <v>-27.7698008</v>
+      </c>
+      <c r="O89">
+        <v>-7.775544223999998</v>
+      </c>
+      <c r="P89">
+        <v>-19.99425657600001</v>
+      </c>
+      <c r="Q89">
+        <v>-21.68425657600001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.2884242957764298</v>
+      </c>
+      <c r="T89">
+        <v>4.22073305535631</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.01606256618001299</v>
+      </c>
+      <c r="W89">
+        <v>0.2349642591962129</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.0573663077857608</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2439140639516411</v>
+      </c>
+      <c r="C90">
+        <v>-105.7553730596419</v>
+      </c>
+      <c r="D90">
+        <v>18.40362694035809</v>
+      </c>
+      <c r="E90">
+        <v>62.084</v>
+      </c>
+      <c r="F90">
+        <v>124.784</v>
+      </c>
+      <c r="G90">
+        <v>0.625</v>
+      </c>
+      <c r="H90">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0</v>
+      </c>
+      <c r="K90">
+        <v>-1.69</v>
+      </c>
+      <c r="L90">
+        <v>1.69</v>
+      </c>
+      <c r="M90">
+        <v>29.7984192</v>
+      </c>
+      <c r="N90">
+        <v>-28.1084192</v>
+      </c>
+      <c r="O90">
+        <v>-7.870357375999998</v>
+      </c>
+      <c r="P90">
+        <v>-20.238061824</v>
+      </c>
+      <c r="Q90">
+        <v>-21.928061824</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.3092263204244657</v>
+      </c>
+      <c r="T90">
+        <v>4.572460809969336</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.01588003701887648</v>
+      </c>
+      <c r="W90">
+        <v>0.2350078471598923</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.05671441792455889</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2459140639516411</v>
+      </c>
+      <c r="C91">
+        <v>-107.3510879534471</v>
+      </c>
+      <c r="D91">
+        <v>18.22591204655294</v>
+      </c>
+      <c r="E91">
+        <v>63.50200000000001</v>
+      </c>
+      <c r="F91">
+        <v>126.202</v>
+      </c>
+      <c r="G91">
+        <v>0.625</v>
+      </c>
+      <c r="H91">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0</v>
+      </c>
+      <c r="K91">
+        <v>-1.69</v>
+      </c>
+      <c r="L91">
+        <v>1.69</v>
+      </c>
+      <c r="M91">
+        <v>30.1370376</v>
+      </c>
+      <c r="N91">
+        <v>-28.4470376</v>
+      </c>
+      <c r="O91">
+        <v>-7.965170527999998</v>
+      </c>
+      <c r="P91">
+        <v>-20.481867072</v>
+      </c>
+      <c r="Q91">
+        <v>-22.171867072</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.3338105313721443</v>
+      </c>
+      <c r="T91">
+        <v>4.988139065421094</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.01570160963664192</v>
+      </c>
+      <c r="W91">
+        <v>0.2350504556187699</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.05607717727372119</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2479140639516411</v>
+      </c>
+      <c r="C92">
+        <v>-108.9434034605166</v>
+      </c>
+      <c r="D92">
+        <v>18.05159653948339</v>
+      </c>
+      <c r="E92">
+        <v>64.92000000000002</v>
+      </c>
+      <c r="F92">
+        <v>127.62</v>
+      </c>
+      <c r="G92">
+        <v>0.625</v>
+      </c>
+      <c r="H92">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0</v>
+      </c>
+      <c r="K92">
+        <v>-1.69</v>
+      </c>
+      <c r="L92">
+        <v>1.69</v>
+      </c>
+      <c r="M92">
+        <v>30.475656</v>
+      </c>
+      <c r="N92">
+        <v>-28.785656</v>
+      </c>
+      <c r="O92">
+        <v>-8.059983679999998</v>
+      </c>
+      <c r="P92">
+        <v>-20.72567232</v>
+      </c>
+      <c r="Q92">
+        <v>-22.41567232000001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.3633115845093589</v>
+      </c>
+      <c r="T92">
+        <v>5.486952971963205</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.0155271473073459</v>
+      </c>
+      <c r="W92">
+        <v>0.2350921172230058</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.05545409752623542</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2499140639516411</v>
+      </c>
+      <c r="C93">
+        <v>-110.5324161936486</v>
+      </c>
+      <c r="D93">
+        <v>17.88058380635143</v>
+      </c>
+      <c r="E93">
+        <v>66.33800000000001</v>
+      </c>
+      <c r="F93">
+        <v>129.038</v>
+      </c>
+      <c r="G93">
+        <v>0.625</v>
+      </c>
+      <c r="H93">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0</v>
+      </c>
+      <c r="K93">
+        <v>-1.69</v>
+      </c>
+      <c r="L93">
+        <v>1.69</v>
+      </c>
+      <c r="M93">
+        <v>30.81427440000001</v>
+      </c>
+      <c r="N93">
+        <v>-29.1242744</v>
+      </c>
+      <c r="O93">
+        <v>-8.154796831999999</v>
+      </c>
+      <c r="P93">
+        <v>-20.96947756800001</v>
+      </c>
+      <c r="Q93">
+        <v>-22.65947756800001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.399368427232621</v>
+      </c>
+      <c r="T93">
+        <v>6.09661441329245</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.01535651931495748</v>
+      </c>
+      <c r="W93">
+        <v>0.2351328631875882</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.05484471183913386</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2519140639516411</v>
+      </c>
+      <c r="C94">
+        <v>-112.1182191389334</v>
+      </c>
+      <c r="D94">
+        <v>17.71278086106661</v>
+      </c>
+      <c r="E94">
+        <v>67.75600000000001</v>
+      </c>
+      <c r="F94">
+        <v>130.456</v>
+      </c>
+      <c r="G94">
+        <v>0.625</v>
+      </c>
+      <c r="H94">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0</v>
+      </c>
+      <c r="K94">
+        <v>-1.69</v>
+      </c>
+      <c r="L94">
+        <v>1.69</v>
+      </c>
+      <c r="M94">
+        <v>31.15289280000001</v>
+      </c>
+      <c r="N94">
+        <v>-29.46289280000001</v>
+      </c>
+      <c r="O94">
+        <v>-8.249609983999999</v>
+      </c>
+      <c r="P94">
+        <v>-21.21328281600001</v>
+      </c>
+      <c r="Q94">
+        <v>-22.90328281600001</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.4444394806366987</v>
+      </c>
+      <c r="T94">
+        <v>6.858691214954008</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.01518960062675142</v>
+      </c>
+      <c r="W94">
+        <v>0.2351727233703318</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.05424857366696945</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2539140639516412</v>
+      </c>
+      <c r="C95">
+        <v>-113.7009018243486</v>
+      </c>
+      <c r="D95">
+        <v>17.5480981756514</v>
+      </c>
+      <c r="E95">
+        <v>69.17400000000002</v>
+      </c>
+      <c r="F95">
+        <v>131.874</v>
+      </c>
+      <c r="G95">
+        <v>0.625</v>
+      </c>
+      <c r="H95">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0</v>
+      </c>
+      <c r="K95">
+        <v>-1.69</v>
+      </c>
+      <c r="L95">
+        <v>1.69</v>
+      </c>
+      <c r="M95">
+        <v>31.49151120000001</v>
+      </c>
+      <c r="N95">
+        <v>-29.80151120000001</v>
+      </c>
+      <c r="O95">
+        <v>-8.344423136</v>
+      </c>
+      <c r="P95">
+        <v>-21.45708806400001</v>
+      </c>
+      <c r="Q95">
+        <v>-23.14708806400001</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.5023879778705129</v>
+      </c>
+      <c r="T95">
+        <v>7.838504245661724</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.01502627158775409</v>
+      </c>
+      <c r="W95">
+        <v>0.2352117263448444</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.05366525567055036</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2559140639516411</v>
+      </c>
+      <c r="C96">
+        <v>-115.2805504790351</v>
+      </c>
+      <c r="D96">
+        <v>17.3864495209649</v>
+      </c>
+      <c r="E96">
+        <v>70.59200000000003</v>
+      </c>
+      <c r="F96">
+        <v>133.292</v>
+      </c>
+      <c r="G96">
+        <v>0.625</v>
+      </c>
+      <c r="H96">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0</v>
+      </c>
+      <c r="K96">
+        <v>-1.69</v>
+      </c>
+      <c r="L96">
+        <v>1.69</v>
+      </c>
+      <c r="M96">
+        <v>31.83012960000001</v>
+      </c>
+      <c r="N96">
+        <v>-30.14012960000001</v>
+      </c>
+      <c r="O96">
+        <v>-8.439236288</v>
+      </c>
+      <c r="P96">
+        <v>-21.70089331200001</v>
+      </c>
+      <c r="Q96">
+        <v>-23.39089331200001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.579652640848932</v>
+      </c>
+      <c r="T96">
+        <v>9.144921619938682</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.01486641763469288</v>
+      </c>
+      <c r="W96">
+        <v>0.2352498994688353</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.05309434869533181</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2579140639516411</v>
+      </c>
+      <c r="C97">
+        <v>-116.8572481838506</v>
+      </c>
+      <c r="D97">
+        <v>17.22775181614937</v>
+      </c>
+      <c r="E97">
+        <v>72.01000000000001</v>
+      </c>
+      <c r="F97">
+        <v>134.71</v>
+      </c>
+      <c r="G97">
+        <v>0.625</v>
+      </c>
+      <c r="H97">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
+      <c r="K97">
+        <v>-1.69</v>
+      </c>
+      <c r="L97">
+        <v>1.69</v>
+      </c>
+      <c r="M97">
+        <v>32.168748</v>
+      </c>
+      <c r="N97">
+        <v>-30.478748</v>
+      </c>
+      <c r="O97">
+        <v>-8.534049439999997</v>
+      </c>
+      <c r="P97">
+        <v>-21.94469856</v>
+      </c>
+      <c r="Q97">
+        <v>-23.63469856</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.6878231690187184</v>
+      </c>
+      <c r="T97">
+        <v>10.97390594392642</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.0147099290280119</v>
+      </c>
+      <c r="W97">
+        <v>0.2352872689481108</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.05253546081432825</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2599140639516411</v>
+      </c>
+      <c r="C98">
+        <v>-118.4310750137525</v>
+      </c>
+      <c r="D98">
+        <v>17.07192498624751</v>
+      </c>
+      <c r="E98">
+        <v>73.42800000000001</v>
+      </c>
+      <c r="F98">
+        <v>136.128</v>
+      </c>
+      <c r="G98">
+        <v>0.625</v>
+      </c>
+      <c r="H98">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0</v>
+      </c>
+      <c r="K98">
+        <v>-1.69</v>
+      </c>
+      <c r="L98">
+        <v>1.69</v>
+      </c>
+      <c r="M98">
+        <v>32.5073664</v>
+      </c>
+      <c r="N98">
+        <v>-30.8173664</v>
+      </c>
+      <c r="O98">
+        <v>-8.628862591999997</v>
+      </c>
+      <c r="P98">
+        <v>-22.188503808</v>
+      </c>
+      <c r="Q98">
+        <v>-23.878503808</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>0.8500789612733963</v>
+      </c>
+      <c r="T98">
+        <v>13.717382429908</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.01455670060063678</v>
+      </c>
+      <c r="W98">
+        <v>0.235323859896568</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.05198821643084572</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2619140639516411</v>
+      </c>
+      <c r="C99">
+        <v>-120.0021081725224</v>
+      </c>
+      <c r="D99">
+        <v>16.91889182747767</v>
+      </c>
+      <c r="E99">
+        <v>74.84600000000002</v>
+      </c>
+      <c r="F99">
+        <v>137.546</v>
+      </c>
+      <c r="G99">
+        <v>0.625</v>
+      </c>
+      <c r="H99">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0</v>
+      </c>
+      <c r="K99">
+        <v>-1.69</v>
+      </c>
+      <c r="L99">
+        <v>1.69</v>
+      </c>
+      <c r="M99">
+        <v>32.8459848</v>
+      </c>
+      <c r="N99">
+        <v>-31.1559848</v>
+      </c>
+      <c r="O99">
+        <v>-8.723675743999998</v>
+      </c>
+      <c r="P99">
+        <v>-22.432309056</v>
+      </c>
+      <c r="Q99">
+        <v>-24.12230905600001</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.120505281697862</v>
+      </c>
+      <c r="T99">
+        <v>18.28984323987733</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.0144066315222797</v>
+      </c>
+      <c r="W99">
+        <v>0.2353596963924796</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.05145225543671328</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2639140639516411</v>
+      </c>
+      <c r="C100">
+        <v>-121.5704221203094</v>
+      </c>
+      <c r="D100">
+        <v>16.76857787969064</v>
+      </c>
+      <c r="E100">
+        <v>76.264</v>
+      </c>
+      <c r="F100">
+        <v>138.964</v>
+      </c>
+      <c r="G100">
+        <v>0.625</v>
+      </c>
+      <c r="H100">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0</v>
+      </c>
+      <c r="K100">
+        <v>-1.69</v>
+      </c>
+      <c r="L100">
+        <v>1.69</v>
+      </c>
+      <c r="M100">
+        <v>33.1846032</v>
+      </c>
+      <c r="N100">
+        <v>-31.4946032</v>
+      </c>
+      <c r="O100">
+        <v>-8.818488895999996</v>
+      </c>
+      <c r="P100">
+        <v>-22.676114304</v>
+      </c>
+      <c r="Q100">
+        <v>-24.366114304</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>1.661357922546793</v>
+      </c>
+      <c r="T100">
+        <v>27.434764859816</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.0142596250781748</v>
+      </c>
+      <c r="W100">
+        <v>0.2353948015313319</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.05092723242205288</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2659140639516411</v>
+      </c>
+      <c r="C101">
+        <v>-123.1360886944345</v>
+      </c>
+      <c r="D101">
+        <v>16.62091130556548</v>
+      </c>
+      <c r="E101">
+        <v>77.682</v>
+      </c>
+      <c r="F101">
+        <v>140.382</v>
+      </c>
+      <c r="G101">
+        <v>0.625</v>
+      </c>
+      <c r="H101">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+      <c r="K101">
+        <v>-1.69</v>
+      </c>
+      <c r="L101">
+        <v>1.69</v>
+      </c>
+      <c r="M101">
+        <v>33.5232216</v>
+      </c>
+      <c r="N101">
+        <v>-31.8332216</v>
+      </c>
+      <c r="O101">
+        <v>-8.913302047999997</v>
+      </c>
+      <c r="P101">
+        <v>-22.919919552</v>
+      </c>
+      <c r="Q101">
+        <v>-24.609919552</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>3.283915845093586</v>
+      </c>
+      <c r="T101">
+        <v>54.86952971963199</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.01411558846122354</v>
+      </c>
+      <c r="W101">
+        <v>0.2354291974754598</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.05041281593294134</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
